--- a/rtss-mexico/src/main/resources/Latin-America-Population.xlsx
+++ b/rtss-mexico/src/main/resources/Latin-America-Population.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-mexico\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5FCDCF-68F3-48D3-91B9-EFB92F8E318F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7645E3-7FA5-4045-9628-EB5C6C643DCB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19710" yWindow="990" windowWidth="17985" windowHeight="21885" xr2:uid="{0C6DB7CF-7936-4F84-A18A-9F2841EE8776}"/>
+    <workbookView xWindow="915" yWindow="1095" windowWidth="17985" windowHeight="21885" activeTab="1" xr2:uid="{0C6DB7CF-7936-4F84-A18A-9F2841EE8776}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Statistical Abstract of Latin America (vol 38, 2002), UCLA Latin America Center Publications, стр. 150-159</t>
   </si>
@@ -116,6 +116,18 @@
   </si>
   <si>
     <t>Значения для большинства стран даны на середину календарного года</t>
+  </si>
+  <si>
+    <t>Исторические данные за 1900-1950 приведены по</t>
+  </si>
+  <si>
+    <t>Statistical Abstract ofLatin America, Supplement 3 (1974) "Statistics and National Policy", UCLA Latin American Center, стр. 173-187</t>
+  </si>
+  <si>
+    <t>далее по UN Demographic Yearbook, отдельные годы по UN Population Division и МВФ</t>
+  </si>
+  <si>
+    <t>где они даны с дополнительным десятичным знаком</t>
   </si>
 </sst>
 </file>
@@ -489,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3493652F-D782-4B7C-88EB-67D8DCBAAE8F}">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -525,6 +537,26 @@
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -758,7 +790,7 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4">
-        <f t="shared" ref="A4:A65" si="0">A3+1</f>
+        <f t="shared" ref="A4:A52" si="0">A3+1</f>
         <v>1902</v>
       </c>
       <c r="B4" s="2">
@@ -3890,6 +3922,9 @@
       <c r="J51" s="2">
         <v>3.1</v>
       </c>
+      <c r="K51" s="2">
+        <v>1.84</v>
+      </c>
       <c r="L51" s="2">
         <v>2.72</v>
       </c>
@@ -4017,7 +4052,7 @@
         <v>2.31</v>
       </c>
       <c r="J53" s="2">
-        <v>1.9</v>
+        <v>3.25</v>
       </c>
       <c r="K53" s="2">
         <v>1.9</v>
@@ -4055,7 +4090,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54">
-        <f t="shared" ref="A54:A117" si="1">A53+1</f>
+        <f t="shared" ref="A54:A102" si="1">A53+1</f>
         <v>1952</v>
       </c>
       <c r="B54" s="2">
@@ -4083,7 +4118,7 @@
         <v>2.29</v>
       </c>
       <c r="J54" s="2">
-        <v>1.97</v>
+        <v>3.43</v>
       </c>
       <c r="K54" s="2">
         <v>1.97</v>
@@ -4149,7 +4184,7 @@
         <v>2.37</v>
       </c>
       <c r="J55" s="2">
-        <v>2.02</v>
+        <v>3.53</v>
       </c>
       <c r="K55" s="2">
         <v>2.02</v>
@@ -4215,7 +4250,7 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="J56" s="2">
-        <v>2.08</v>
+        <v>3.64</v>
       </c>
       <c r="K56" s="2">
         <v>2.08</v>
@@ -4281,7 +4316,7 @@
         <v>2.54</v>
       </c>
       <c r="J57" s="2">
-        <v>2.14</v>
+        <v>3.75</v>
       </c>
       <c r="K57" s="2">
         <v>2.14</v>
@@ -4347,7 +4382,7 @@
         <v>2.63</v>
       </c>
       <c r="J58" s="2">
-        <v>2.2000000000000002</v>
+        <v>3.87</v>
       </c>
       <c r="K58" s="2">
         <v>2.2000000000000002</v>
@@ -4413,7 +4448,7 @@
         <v>2.73</v>
       </c>
       <c r="J59" s="2">
-        <v>2.2599999999999998</v>
+        <v>3.98</v>
       </c>
       <c r="K59" s="2">
         <v>2.2599999999999998</v>
@@ -4479,7 +4514,7 @@
         <v>2.83</v>
       </c>
       <c r="J60" s="2">
-        <v>2.3199999999999998</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="K60" s="2">
         <v>2.3199999999999998</v>
@@ -4545,7 +4580,7 @@
         <v>2.93</v>
       </c>
       <c r="J61" s="2">
-        <v>2.39</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="K61" s="2">
         <v>2.39</v>
@@ -4611,7 +4646,7 @@
         <v>3.04</v>
       </c>
       <c r="J62" s="2">
-        <v>2.4500000000000002</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="K62" s="2">
         <v>2.4500000000000002</v>
@@ -4677,7 +4712,7 @@
         <v>3.12</v>
       </c>
       <c r="J63" s="2">
-        <v>2.5099999999999998</v>
+        <v>4.5</v>
       </c>
       <c r="K63" s="2">
         <v>2.5099999999999998</v>
@@ -4743,7 +4778,7 @@
         <v>3.21</v>
       </c>
       <c r="J64" s="2">
-        <v>2.63</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="K64" s="2">
         <v>2.63</v>
@@ -4809,7 +4844,7 @@
         <v>3.31</v>
       </c>
       <c r="J65" s="2">
-        <v>2.72</v>
+        <v>4.78</v>
       </c>
       <c r="K65" s="2">
         <v>2.72</v>
@@ -4875,7 +4910,7 @@
         <v>3.41</v>
       </c>
       <c r="J66" s="2">
-        <v>2.82</v>
+        <v>4.93</v>
       </c>
       <c r="K66" s="2">
         <v>2.82</v>
@@ -4941,7 +4976,7 @@
         <v>3.51</v>
       </c>
       <c r="J67" s="2">
-        <v>2.93</v>
+        <v>5.07</v>
       </c>
       <c r="K67" s="2">
         <v>2.93</v>
@@ -5007,7 +5042,7 @@
         <v>3.62</v>
       </c>
       <c r="J68" s="2">
-        <v>3.04</v>
+        <v>5.22</v>
       </c>
       <c r="K68" s="2">
         <v>3.04</v>
@@ -5073,7 +5108,7 @@
         <v>3.72</v>
       </c>
       <c r="J69" s="2">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="K69" s="2">
         <v>3.15</v>
@@ -5139,7 +5174,7 @@
         <v>3.83</v>
       </c>
       <c r="J70" s="2">
-        <v>3.27</v>
+        <v>5.58</v>
       </c>
       <c r="K70" s="2">
         <v>3.27</v>
@@ -5205,7 +5240,7 @@
         <v>3.95</v>
       </c>
       <c r="J71" s="2">
-        <v>3.36</v>
+        <v>5.77</v>
       </c>
       <c r="K71" s="2">
         <v>3.36</v>
@@ -5271,7 +5306,7 @@
         <v>4.0599999999999996</v>
       </c>
       <c r="J72" s="2">
-        <v>3.44</v>
+        <v>5.96</v>
       </c>
       <c r="K72" s="2">
         <v>3.44</v>
@@ -5337,7 +5372,7 @@
         <v>4.18</v>
       </c>
       <c r="J73" s="2">
-        <v>3.55</v>
+        <v>6.17</v>
       </c>
       <c r="K73" s="2">
         <v>3.55</v>
@@ -5403,7 +5438,7 @@
         <v>4.3</v>
       </c>
       <c r="J74" s="2">
-        <v>3.67</v>
+        <v>6.38</v>
       </c>
       <c r="K74" s="2">
         <v>3.67</v>
@@ -5469,7 +5504,7 @@
         <v>4.43</v>
       </c>
       <c r="J75" s="2">
-        <v>3.77</v>
+        <v>6.6</v>
       </c>
       <c r="K75" s="2">
         <v>3.77</v>
@@ -5535,7 +5570,7 @@
         <v>4.5599999999999996</v>
       </c>
       <c r="J76" s="2">
-        <v>3.89</v>
+        <v>6.83</v>
       </c>
       <c r="K76" s="2">
         <v>3.89</v>
@@ -5601,7 +5636,7 @@
         <v>4.7</v>
       </c>
       <c r="J77" s="2">
-        <v>4.01</v>
+        <v>7.03</v>
       </c>
       <c r="K77" s="2">
         <v>4.01</v>
@@ -5667,7 +5702,7 @@
         <v>4.8899999999999997</v>
       </c>
       <c r="J78" s="2">
-        <v>4.12</v>
+        <v>7.24</v>
       </c>
       <c r="K78" s="2">
         <v>4.12</v>
@@ -5733,7 +5768,7 @@
         <v>5.03</v>
       </c>
       <c r="J79" s="2">
-        <v>4.26</v>
+        <v>7.45</v>
       </c>
       <c r="K79" s="2">
         <v>4.26</v>
@@ -5799,7 +5834,7 @@
         <v>5.17</v>
       </c>
       <c r="J80" s="2">
-        <v>4.3499999999999996</v>
+        <v>7.67</v>
       </c>
       <c r="K80" s="2">
         <v>4.3499999999999996</v>
@@ -5865,7 +5900,7 @@
         <v>5.3</v>
       </c>
       <c r="J81" s="2">
-        <v>4.4400000000000004</v>
+        <v>7.89</v>
       </c>
       <c r="K81" s="2">
         <v>4.4400000000000004</v>
@@ -5931,7 +5966,7 @@
         <v>5.44</v>
       </c>
       <c r="J82" s="2">
-        <v>4.51</v>
+        <v>8.1199999999999992</v>
       </c>
       <c r="K82" s="2">
         <v>4.51</v>
@@ -5997,7 +6032,7 @@
         <v>5.58</v>
       </c>
       <c r="J83" s="2">
-        <v>4.59</v>
+        <v>8.36</v>
       </c>
       <c r="K83" s="2">
         <v>4.59</v>
@@ -6063,7 +6098,7 @@
         <v>5.98</v>
       </c>
       <c r="J84" s="2">
-        <v>4.66</v>
+        <v>8.61</v>
       </c>
       <c r="K84" s="2">
         <v>4.66</v>
@@ -6129,7 +6164,7 @@
         <v>6.12</v>
       </c>
       <c r="J85" s="2">
-        <v>4.72</v>
+        <v>8.86</v>
       </c>
       <c r="K85" s="2">
         <v>4.72</v>
@@ -6195,7 +6230,7 @@
         <v>6.27</v>
       </c>
       <c r="J86" s="2">
-        <v>4.78</v>
+        <v>8.8699999999999992</v>
       </c>
       <c r="K86" s="2">
         <v>4.78</v>
@@ -6261,7 +6296,7 @@
         <v>6.42</v>
       </c>
       <c r="J87" s="2">
-        <v>4.8600000000000003</v>
+        <v>9.1</v>
       </c>
       <c r="K87" s="2">
         <v>4.8600000000000003</v>
@@ -6327,7 +6362,7 @@
         <v>6.57</v>
       </c>
       <c r="J88" s="2">
-        <v>4.95</v>
+        <v>9.33</v>
       </c>
       <c r="K88" s="2">
         <v>4.95</v>
@@ -6393,7 +6428,7 @@
         <v>6.72</v>
       </c>
       <c r="J89" s="2">
-        <v>5.05</v>
+        <v>9.56</v>
       </c>
       <c r="K89" s="2">
         <v>5.05</v>
@@ -6459,7 +6494,7 @@
         <v>6.87</v>
       </c>
       <c r="J90" s="2">
-        <v>5.09</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="K90" s="2">
         <v>5.09</v>
@@ -6525,7 +6560,7 @@
         <v>7.02</v>
       </c>
       <c r="J91" s="2">
-        <v>5.19</v>
+        <v>10.029999999999999</v>
       </c>
       <c r="K91" s="2">
         <v>5.19</v>
@@ -6591,7 +6626,7 @@
         <v>7.17</v>
       </c>
       <c r="J92" s="2">
-        <v>5.1100000000000003</v>
+        <v>10.26</v>
       </c>
       <c r="K92" s="2">
         <v>5.1100000000000003</v>
@@ -6657,7 +6692,7 @@
         <v>7.32</v>
       </c>
       <c r="J93" s="2">
-        <v>5.35</v>
+        <v>10.5</v>
       </c>
       <c r="K93" s="2">
         <v>5.35</v>
@@ -6723,7 +6758,7 @@
         <v>7.47</v>
       </c>
       <c r="J94" s="2">
-        <v>5.48</v>
+        <v>10.74</v>
       </c>
       <c r="K94" s="2">
         <v>5.48</v>
@@ -6789,7 +6824,7 @@
         <v>7.62</v>
       </c>
       <c r="J95" s="2">
-        <v>5.43</v>
+        <v>10.98</v>
       </c>
       <c r="K95" s="2">
         <v>5.43</v>
@@ -6855,7 +6890,7 @@
         <v>7.77</v>
       </c>
       <c r="J96" s="2">
-        <v>5.55</v>
+        <v>11.22</v>
       </c>
       <c r="K96" s="2">
         <v>5.55</v>
@@ -6921,7 +6956,7 @@
         <v>7.92</v>
       </c>
       <c r="J97" s="2">
-        <v>5.67</v>
+        <v>11.46</v>
       </c>
       <c r="K97" s="2">
         <v>5.67</v>
@@ -6987,7 +7022,7 @@
         <v>8.0500000000000007</v>
       </c>
       <c r="J98" s="2">
-        <v>5.79</v>
+        <v>11.7</v>
       </c>
       <c r="K98" s="2">
         <v>5.79</v>
@@ -7053,7 +7088,7 @@
         <v>8.1</v>
       </c>
       <c r="J99" s="2">
-        <v>5.91</v>
+        <v>11.94</v>
       </c>
       <c r="K99" s="2">
         <v>5.91</v>
@@ -7119,7 +7154,7 @@
         <v>8.1</v>
       </c>
       <c r="J100" s="2">
-        <v>6.03</v>
+        <v>12.17</v>
       </c>
       <c r="K100" s="2">
         <v>6.03</v>
@@ -7185,7 +7220,7 @@
         <v>8.36</v>
       </c>
       <c r="J101" s="2">
-        <v>6.15</v>
+        <v>12.41</v>
       </c>
       <c r="K101" s="2">
         <v>6.15</v>
@@ -7251,7 +7286,7 @@
         <v>8.5</v>
       </c>
       <c r="J102" s="2">
-        <v>6.28</v>
+        <v>12.65</v>
       </c>
       <c r="K102" s="2">
         <v>6.28</v>

--- a/rtss-mexico/src/main/resources/Latin-America-Population.xlsx
+++ b/rtss-mexico/src/main/resources/Latin-America-Population.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-mexico\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7645E3-7FA5-4045-9628-EB5C6C643DCB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B199E647-ADC5-4152-B6B7-175CA9B9E15C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="915" yWindow="1095" windowWidth="17985" windowHeight="21885" activeTab="1" xr2:uid="{0C6DB7CF-7936-4F84-A18A-9F2841EE8776}"/>
+    <workbookView xWindow="60" yWindow="360" windowWidth="19125" windowHeight="23055" xr2:uid="{0C6DB7CF-7936-4F84-A18A-9F2841EE8776}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
-    <sheet name="Data" sheetId="1" r:id="rId2"/>
+    <sheet name="Data-2002" sheetId="1" r:id="rId2"/>
+    <sheet name="Data-1974" sheetId="3" r:id="rId3"/>
+    <sheet name="Data-Alt" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="59">
   <si>
     <t>Statistical Abstract of Latin America (vol 38, 2002), UCLA Latin America Center Publications, стр. 150-159</t>
   </si>
@@ -129,12 +131,93 @@
   <si>
     <t>где они даны с дополнительным десятичным знаком</t>
   </si>
+  <si>
+    <t>Data-2002</t>
+  </si>
+  <si>
+    <t>Data-1974</t>
+  </si>
+  <si>
+    <t>notes:</t>
+  </si>
+  <si>
+    <t>Боливия: включает оценку живущих в джунглях</t>
+  </si>
+  <si>
+    <t>Колумбия:</t>
+  </si>
+  <si>
+    <t>The 1928 census was not accepted by the Colombian National Congress because census was believed to be inflated for certain civil divisions.</t>
+  </si>
+  <si>
+    <t>The 1905 census has been the subject of controversy; for discussion which accepts a revised estimate of 4355, see J de D Higuita, "Estudio Historico Anali'tico de la Poblacion Colombiana en 170 Anos,” Anales de Economia Estadistica; Boletin de la Contraloria General 3:2 (April 1940), Suplemento (published by Colombia, Contraloria General, Direccion Nacional de Estadistica). In any case, total excludes Panama.</t>
+  </si>
+  <si>
+    <t>Excluding Canal Zone; including estimates for jungle Indians.</t>
+  </si>
+  <si>
+    <t>Панама:</t>
+  </si>
+  <si>
+    <t>Data-Alt -- Альтернативные оценки по декадам</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources: </t>
+  </si>
+  <si>
+    <t>O. Andrew Collver, Birth Rates in Latin America: New Estimates of Historical Trends and Fluctuations, passim</t>
+  </si>
+  <si>
+    <t>United Nations, World Population Prospects as Assessed in 1963 (New York: Department of Economic and Social Affairs, 1966), pp. 143-144</t>
+  </si>
+  <si>
+    <t>страна</t>
+  </si>
+  <si>
+    <t>Латинская Америка</t>
+  </si>
+  <si>
+    <t>Аргениина</t>
+  </si>
+  <si>
+    <t>Коста Рика</t>
+  </si>
+  <si>
+    <t>Эль Сальвадор</t>
+  </si>
+  <si>
+    <t>Гаита</t>
+  </si>
+  <si>
+    <t>Collver</t>
+  </si>
+  <si>
+    <t>WPP</t>
+  </si>
+  <si>
+    <t>SA = Sanchez-Albornoz</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>Желтым цветом помечена неполная сумма по части стран</t>
+  </si>
+  <si>
+    <t>Источники не указывают, включают ли они оценку населения в джунглях</t>
+  </si>
+  <si>
+    <t>Nicolas Sanchez-Albornoz, The Population of Latin America, pp. 169 and 184  - data since 1930 are quoted from Centro Latinoamericano de Demograffa (CELADE), Boletfn Demografico V:10 (1972), pp. 4-5</t>
+  </si>
+  <si>
+    <t>Statistical Abstract ofLatin America, Supplement 3 (1974) "Statistics and National Policy", UCLA Latin American Center, стр. 186</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,8 +233,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -161,6 +265,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -177,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -186,6 +296,34 @@
     </xf>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -501,66 +639,122 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3493652F-D782-4B7C-88EB-67D8DCBAAE8F}">
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A21" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A28" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7326,4 +7520,6301 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D34E3C15-A1AF-4867-A59B-75FEE7825882}">
+  <dimension ref="A1:U85"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>1900</v>
+      </c>
+      <c r="B2" s="7">
+        <v>4607</v>
+      </c>
+      <c r="C2" s="7">
+        <v>1766</v>
+      </c>
+      <c r="D2" s="7">
+        <v>17984</v>
+      </c>
+      <c r="E2" s="7">
+        <v>2959</v>
+      </c>
+      <c r="F2" s="8">
+        <v>3894</v>
+      </c>
+      <c r="G2" s="7">
+        <v>307</v>
+      </c>
+      <c r="H2" s="7">
+        <v>1600</v>
+      </c>
+      <c r="I2" s="7">
+        <v>600</v>
+      </c>
+      <c r="J2" s="7">
+        <v>1300</v>
+      </c>
+      <c r="K2" s="7">
+        <v>801</v>
+      </c>
+      <c r="L2" s="7">
+        <v>885</v>
+      </c>
+      <c r="M2" s="7">
+        <v>1250</v>
+      </c>
+      <c r="N2" s="7">
+        <v>420</v>
+      </c>
+      <c r="O2" s="7">
+        <v>13607</v>
+      </c>
+      <c r="P2" s="7">
+        <v>420</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>263</v>
+      </c>
+      <c r="R2" s="7">
+        <v>490</v>
+      </c>
+      <c r="S2" s="7">
+        <v>3000</v>
+      </c>
+      <c r="T2" s="8">
+        <v>963</v>
+      </c>
+      <c r="U2" s="7">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <f>A2+1</f>
+        <v>1901</v>
+      </c>
+      <c r="B3" s="7">
+        <v>4741</v>
+      </c>
+      <c r="C3" s="7">
+        <v>1785</v>
+      </c>
+      <c r="D3" s="7">
+        <v>18392</v>
+      </c>
+      <c r="E3" s="7">
+        <v>2994</v>
+      </c>
+      <c r="F3" s="8">
+        <v>3944</v>
+      </c>
+      <c r="G3" s="7">
+        <v>313</v>
+      </c>
+      <c r="H3" s="7">
+        <v>1679</v>
+      </c>
+      <c r="I3" s="7">
+        <v>614</v>
+      </c>
+      <c r="J3" s="7">
+        <v>1312</v>
+      </c>
+      <c r="K3" s="7">
+        <v>819</v>
+      </c>
+      <c r="L3" s="7">
+        <v>910</v>
+      </c>
+      <c r="M3" s="7">
+        <v>1294</v>
+      </c>
+      <c r="N3" s="7">
+        <v>436</v>
+      </c>
+      <c r="O3" s="7">
+        <v>13755</v>
+      </c>
+      <c r="P3" s="7">
+        <v>434</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>270</v>
+      </c>
+      <c r="R3" s="7">
+        <v>506</v>
+      </c>
+      <c r="S3" s="7">
+        <v>3100</v>
+      </c>
+      <c r="T3" s="8">
+        <v>965</v>
+      </c>
+      <c r="U3" s="7">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <f t="shared" ref="A4:A65" si="0">A3+1</f>
+        <v>1902</v>
+      </c>
+      <c r="B4" s="7">
+        <v>4872</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1803</v>
+      </c>
+      <c r="D4" s="7">
+        <v>18782</v>
+      </c>
+      <c r="E4" s="7">
+        <v>3030</v>
+      </c>
+      <c r="F4" s="8">
+        <v>3994</v>
+      </c>
+      <c r="G4" s="7">
+        <v>318</v>
+      </c>
+      <c r="H4" s="7">
+        <v>1758</v>
+      </c>
+      <c r="I4" s="7">
+        <v>628</v>
+      </c>
+      <c r="J4" s="7">
+        <v>1324</v>
+      </c>
+      <c r="K4" s="7">
+        <v>838</v>
+      </c>
+      <c r="L4" s="7">
+        <v>936</v>
+      </c>
+      <c r="M4" s="7">
+        <v>1338</v>
+      </c>
+      <c r="N4" s="7">
+        <v>452</v>
+      </c>
+      <c r="O4" s="7">
+        <v>13905</v>
+      </c>
+      <c r="P4" s="7">
+        <v>448</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>276</v>
+      </c>
+      <c r="R4" s="7">
+        <v>522</v>
+      </c>
+      <c r="S4" s="7">
+        <v>3200</v>
+      </c>
+      <c r="T4" s="8">
+        <v>990</v>
+      </c>
+      <c r="U4" s="7">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <f t="shared" si="0"/>
+        <v>1903</v>
+      </c>
+      <c r="B5" s="7">
+        <v>4976</v>
+      </c>
+      <c r="C5" s="7">
+        <v>1822</v>
+      </c>
+      <c r="D5" s="7">
+        <v>19180</v>
+      </c>
+      <c r="E5" s="7">
+        <v>3066</v>
+      </c>
+      <c r="F5" s="8">
+        <v>4044</v>
+      </c>
+      <c r="G5" s="7">
+        <v>324</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1837</v>
+      </c>
+      <c r="I5" s="7">
+        <v>642</v>
+      </c>
+      <c r="J5" s="7">
+        <v>1336</v>
+      </c>
+      <c r="K5" s="7">
+        <v>856</v>
+      </c>
+      <c r="L5" s="7">
+        <v>961</v>
+      </c>
+      <c r="M5" s="7">
+        <v>1381</v>
+      </c>
+      <c r="N5" s="7">
+        <v>468</v>
+      </c>
+      <c r="O5" s="7">
+        <v>14065</v>
+      </c>
+      <c r="P5" s="7">
+        <v>462</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>283</v>
+      </c>
+      <c r="R5" s="7">
+        <v>539</v>
+      </c>
+      <c r="S5" s="7">
+        <v>3300</v>
+      </c>
+      <c r="T5" s="8">
+        <v>1019</v>
+      </c>
+      <c r="U5" s="7">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1904</v>
+      </c>
+      <c r="B6" s="7">
+        <v>5104</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1840</v>
+      </c>
+      <c r="D6" s="7">
+        <v>19587</v>
+      </c>
+      <c r="E6" s="7">
+        <v>3102</v>
+      </c>
+      <c r="F6" s="8">
+        <v>4094</v>
+      </c>
+      <c r="G6" s="7">
+        <v>330</v>
+      </c>
+      <c r="H6" s="7">
+        <v>1879</v>
+      </c>
+      <c r="I6" s="7">
+        <v>656</v>
+      </c>
+      <c r="J6" s="7">
+        <v>1348</v>
+      </c>
+      <c r="K6" s="7">
+        <v>874</v>
+      </c>
+      <c r="L6" s="7">
+        <v>987</v>
+      </c>
+      <c r="M6" s="7">
+        <v>1425</v>
+      </c>
+      <c r="N6" s="7">
+        <v>484</v>
+      </c>
+      <c r="O6" s="7">
+        <v>14208</v>
+      </c>
+      <c r="P6" s="7">
+        <v>477</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>290</v>
+      </c>
+      <c r="R6" s="7">
+        <v>555</v>
+      </c>
+      <c r="S6" s="7">
+        <v>3400</v>
+      </c>
+      <c r="T6" s="8">
+        <v>1038</v>
+      </c>
+      <c r="U6" s="7">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <f t="shared" si="0"/>
+        <v>1905</v>
+      </c>
+      <c r="B7" s="7">
+        <v>5290</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1859</v>
+      </c>
+      <c r="D7" s="7">
+        <v>20003</v>
+      </c>
+      <c r="E7" s="7">
+        <v>3139</v>
+      </c>
+      <c r="F7" s="8">
+        <v>4144</v>
+      </c>
+      <c r="G7" s="7">
+        <v>336</v>
+      </c>
+      <c r="H7" s="7">
+        <v>1927</v>
+      </c>
+      <c r="I7" s="7">
+        <v>670</v>
+      </c>
+      <c r="J7" s="7">
+        <v>1360</v>
+      </c>
+      <c r="K7" s="7">
+        <v>893</v>
+      </c>
+      <c r="L7" s="7">
+        <v>1013</v>
+      </c>
+      <c r="M7" s="7">
+        <v>1468</v>
+      </c>
+      <c r="N7" s="7">
+        <v>500</v>
+      </c>
+      <c r="O7" s="7">
+        <v>14363</v>
+      </c>
+      <c r="P7" s="7">
+        <v>491</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>297</v>
+      </c>
+      <c r="R7" s="7">
+        <v>571</v>
+      </c>
+      <c r="S7" s="7">
+        <v>3500</v>
+      </c>
+      <c r="T7" s="8">
+        <v>1071</v>
+      </c>
+      <c r="U7" s="7">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <f t="shared" si="0"/>
+        <v>1906</v>
+      </c>
+      <c r="B8" s="7">
+        <v>5524</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1877</v>
+      </c>
+      <c r="D8" s="7">
+        <v>20427</v>
+      </c>
+      <c r="E8" s="7">
+        <v>3176</v>
+      </c>
+      <c r="F8" s="8">
+        <v>4277</v>
+      </c>
+      <c r="G8" s="7">
+        <v>341</v>
+      </c>
+      <c r="H8" s="7">
+        <v>1979</v>
+      </c>
+      <c r="I8" s="7">
+        <v>684</v>
+      </c>
+      <c r="J8" s="7">
+        <v>1372</v>
+      </c>
+      <c r="K8" s="7">
+        <v>911</v>
+      </c>
+      <c r="L8" s="7">
+        <v>1029</v>
+      </c>
+      <c r="M8" s="7">
+        <v>1512</v>
+      </c>
+      <c r="N8" s="7">
+        <v>511</v>
+      </c>
+      <c r="O8" s="7">
+        <v>14519</v>
+      </c>
+      <c r="P8" s="7">
+        <v>505</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>304</v>
+      </c>
+      <c r="R8" s="7">
+        <v>580</v>
+      </c>
+      <c r="S8" s="7">
+        <v>3600</v>
+      </c>
+      <c r="T8" s="8">
+        <v>1103</v>
+      </c>
+      <c r="U8" s="7">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <f t="shared" si="0"/>
+        <v>1907</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5822</v>
+      </c>
+      <c r="C9" s="7">
+        <v>1896</v>
+      </c>
+      <c r="D9" s="7">
+        <v>20860</v>
+      </c>
+      <c r="E9" s="7">
+        <v>3213</v>
+      </c>
+      <c r="F9" s="8">
+        <v>4409</v>
+      </c>
+      <c r="G9" s="7">
+        <v>347</v>
+      </c>
+      <c r="H9" s="7">
+        <v>2034</v>
+      </c>
+      <c r="I9" s="7">
+        <v>698</v>
+      </c>
+      <c r="J9" s="7">
+        <v>1384</v>
+      </c>
+      <c r="K9" s="7">
+        <v>929</v>
+      </c>
+      <c r="L9" s="7">
+        <v>1046</v>
+      </c>
+      <c r="M9" s="7">
+        <v>1555</v>
+      </c>
+      <c r="N9" s="7">
+        <v>521</v>
+      </c>
+      <c r="O9" s="7">
+        <v>14677</v>
+      </c>
+      <c r="P9" s="7">
+        <v>515</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>311</v>
+      </c>
+      <c r="R9" s="7">
+        <v>590</v>
+      </c>
+      <c r="S9" s="7">
+        <v>3700</v>
+      </c>
+      <c r="T9" s="8">
+        <v>1141</v>
+      </c>
+      <c r="U9" s="7">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <f t="shared" si="0"/>
+        <v>1908</v>
+      </c>
+      <c r="B10" s="7">
+        <v>6145</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1914</v>
+      </c>
+      <c r="D10" s="7">
+        <v>21303</v>
+      </c>
+      <c r="E10" s="7">
+        <v>3253</v>
+      </c>
+      <c r="F10" s="8">
+        <v>4542</v>
+      </c>
+      <c r="G10" s="7">
+        <v>353</v>
+      </c>
+      <c r="H10" s="7">
+        <v>2092</v>
+      </c>
+      <c r="I10" s="7">
+        <v>712</v>
+      </c>
+      <c r="J10" s="7">
+        <v>1396</v>
+      </c>
+      <c r="K10" s="7">
+        <v>948</v>
+      </c>
+      <c r="L10" s="7">
+        <v>1062</v>
+      </c>
+      <c r="M10" s="7">
+        <v>1559</v>
+      </c>
+      <c r="N10" s="7">
+        <v>532</v>
+      </c>
+      <c r="O10" s="7">
+        <v>14836</v>
+      </c>
+      <c r="P10" s="7">
+        <v>524</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>318</v>
+      </c>
+      <c r="R10" s="7">
+        <v>600</v>
+      </c>
+      <c r="S10" s="7">
+        <v>3800</v>
+      </c>
+      <c r="T10" s="8">
+        <v>1054</v>
+      </c>
+      <c r="U10" s="7">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <f t="shared" si="0"/>
+        <v>1909</v>
+      </c>
+      <c r="B11" s="7">
+        <v>6432</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1933</v>
+      </c>
+      <c r="D11" s="7">
+        <v>21754</v>
+      </c>
+      <c r="E11" s="7">
+        <v>3294</v>
+      </c>
+      <c r="F11" s="8">
+        <v>4674</v>
+      </c>
+      <c r="G11" s="7">
+        <v>358</v>
+      </c>
+      <c r="H11" s="7">
+        <v>2154</v>
+      </c>
+      <c r="I11" s="7">
+        <v>726</v>
+      </c>
+      <c r="J11" s="7">
+        <v>1408</v>
+      </c>
+      <c r="K11" s="7">
+        <v>966</v>
+      </c>
+      <c r="L11" s="7">
+        <v>1079</v>
+      </c>
+      <c r="M11" s="7">
+        <v>1643</v>
+      </c>
+      <c r="N11" s="7">
+        <v>542</v>
+      </c>
+      <c r="O11" s="7">
+        <v>14997</v>
+      </c>
+      <c r="P11" s="7">
+        <v>534</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>325</v>
+      </c>
+      <c r="R11" s="7">
+        <v>610</v>
+      </c>
+      <c r="S11" s="7">
+        <v>3900</v>
+      </c>
+      <c r="T11" s="8">
+        <v>1095</v>
+      </c>
+      <c r="U11" s="7">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <f t="shared" si="0"/>
+        <v>1910</v>
+      </c>
+      <c r="B12" s="7">
+        <v>6799</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1951</v>
+      </c>
+      <c r="D12" s="7">
+        <v>22216</v>
+      </c>
+      <c r="E12" s="7">
+        <v>3336</v>
+      </c>
+      <c r="F12" s="8">
+        <v>4807</v>
+      </c>
+      <c r="G12" s="7">
+        <v>364</v>
+      </c>
+      <c r="H12" s="7">
+        <v>2219</v>
+      </c>
+      <c r="I12" s="7">
+        <v>740</v>
+      </c>
+      <c r="J12" s="7">
+        <v>1421</v>
+      </c>
+      <c r="K12" s="7">
+        <v>985</v>
+      </c>
+      <c r="L12" s="7">
+        <v>1096</v>
+      </c>
+      <c r="M12" s="7">
+        <v>1687</v>
+      </c>
+      <c r="N12" s="7">
+        <v>553</v>
+      </c>
+      <c r="O12" s="7">
+        <v>15160</v>
+      </c>
+      <c r="P12" s="7">
+        <v>543</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>332</v>
+      </c>
+      <c r="R12" s="7">
+        <v>620</v>
+      </c>
+      <c r="S12" s="7">
+        <v>4000</v>
+      </c>
+      <c r="T12" s="8">
+        <v>1132</v>
+      </c>
+      <c r="U12" s="7">
+        <v>2596</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <f t="shared" si="0"/>
+        <v>1911</v>
+      </c>
+      <c r="B13" s="7">
+        <v>7070</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1970</v>
+      </c>
+      <c r="D13" s="7">
+        <v>22687</v>
+      </c>
+      <c r="E13" s="7">
+        <v>3378</v>
+      </c>
+      <c r="F13" s="8">
+        <v>4940</v>
+      </c>
+      <c r="G13" s="7">
+        <v>370</v>
+      </c>
+      <c r="H13" s="7">
+        <v>2287</v>
+      </c>
+      <c r="I13" s="7">
+        <v>753</v>
+      </c>
+      <c r="J13" s="7">
+        <v>1433</v>
+      </c>
+      <c r="K13" s="7">
+        <v>1003</v>
+      </c>
+      <c r="L13" s="7">
+        <v>1119</v>
+      </c>
+      <c r="M13" s="7">
+        <v>1730</v>
+      </c>
+      <c r="N13" s="7">
+        <v>562</v>
+      </c>
+      <c r="O13" s="7">
+        <v>15333</v>
+      </c>
+      <c r="P13" s="7">
+        <v>553</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>339</v>
+      </c>
+      <c r="R13" s="7">
+        <v>630</v>
+      </c>
+      <c r="S13" s="7">
+        <v>4100</v>
+      </c>
+      <c r="T13" s="8">
+        <v>1178</v>
+      </c>
+      <c r="U13" s="7">
+        <v>2612</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <f t="shared" si="0"/>
+        <v>1912</v>
+      </c>
+      <c r="B14" s="7">
+        <v>7467</v>
+      </c>
+      <c r="C14" s="7">
+        <v>1988</v>
+      </c>
+      <c r="D14" s="7">
+        <v>23168</v>
+      </c>
+      <c r="E14" s="7">
+        <v>3421</v>
+      </c>
+      <c r="F14" s="8">
+        <v>5072</v>
+      </c>
+      <c r="G14" s="7">
+        <v>375</v>
+      </c>
+      <c r="H14" s="7">
+        <v>2358</v>
+      </c>
+      <c r="I14" s="7">
+        <v>767</v>
+      </c>
+      <c r="J14" s="7">
+        <v>1445</v>
+      </c>
+      <c r="K14" s="7">
+        <v>1021</v>
+      </c>
+      <c r="L14" s="7">
+        <v>1142</v>
+      </c>
+      <c r="M14" s="7">
+        <v>1774</v>
+      </c>
+      <c r="N14" s="7">
+        <v>571</v>
+      </c>
+      <c r="O14" s="7">
+        <v>15508</v>
+      </c>
+      <c r="P14" s="7">
+        <v>562</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>352</v>
+      </c>
+      <c r="R14" s="7">
+        <v>640</v>
+      </c>
+      <c r="S14" s="7">
+        <v>4187</v>
+      </c>
+      <c r="T14" s="8">
+        <v>1226</v>
+      </c>
+      <c r="U14" s="7">
+        <v>2639</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <f t="shared" si="0"/>
+        <v>1913</v>
+      </c>
+      <c r="B15" s="7">
+        <v>7838</v>
+      </c>
+      <c r="C15" s="7">
+        <v>2007</v>
+      </c>
+      <c r="D15" s="7">
+        <v>23660</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3465</v>
+      </c>
+      <c r="F15" s="8">
+        <v>5193</v>
+      </c>
+      <c r="G15" s="7">
+        <v>381</v>
+      </c>
+      <c r="H15" s="7">
+        <v>2413</v>
+      </c>
+      <c r="I15" s="7">
+        <v>781</v>
+      </c>
+      <c r="J15" s="7">
+        <v>1457</v>
+      </c>
+      <c r="K15" s="7">
+        <v>1040</v>
+      </c>
+      <c r="L15" s="7">
+        <v>1165</v>
+      </c>
+      <c r="M15" s="7">
+        <v>1818</v>
+      </c>
+      <c r="N15" s="7">
+        <v>579</v>
+      </c>
+      <c r="O15" s="7">
+        <v>15373</v>
+      </c>
+      <c r="P15" s="7">
+        <v>572</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>364</v>
+      </c>
+      <c r="R15" s="7">
+        <v>650</v>
+      </c>
+      <c r="S15" s="7">
+        <v>4267</v>
+      </c>
+      <c r="T15" s="8">
+        <v>1279</v>
+      </c>
+      <c r="U15" s="7">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <f t="shared" si="0"/>
+        <v>1914</v>
+      </c>
+      <c r="B16" s="7">
+        <v>7996</v>
+      </c>
+      <c r="C16" s="7">
+        <v>2025</v>
+      </c>
+      <c r="D16" s="7">
+        <v>24161</v>
+      </c>
+      <c r="E16" s="7">
+        <v>3509</v>
+      </c>
+      <c r="F16" s="8">
+        <v>5318</v>
+      </c>
+      <c r="G16" s="7">
+        <v>387</v>
+      </c>
+      <c r="H16" s="7">
+        <v>2507</v>
+      </c>
+      <c r="I16" s="7">
+        <v>795</v>
+      </c>
+      <c r="J16" s="7">
+        <v>1469</v>
+      </c>
+      <c r="K16" s="7">
+        <v>1058</v>
+      </c>
+      <c r="L16" s="7">
+        <v>1180</v>
+      </c>
+      <c r="M16" s="7">
+        <v>1862</v>
+      </c>
+      <c r="N16" s="7">
+        <v>588</v>
+      </c>
+      <c r="O16" s="7">
+        <v>15083</v>
+      </c>
+      <c r="P16" s="7">
+        <v>581</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>378</v>
+      </c>
+      <c r="R16" s="7">
+        <v>657</v>
+      </c>
+      <c r="S16" s="7">
+        <v>4347</v>
+      </c>
+      <c r="T16" s="8">
+        <v>1316</v>
+      </c>
+      <c r="U16" s="7">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <f t="shared" si="0"/>
+        <v>1915</v>
+      </c>
+      <c r="B17" s="7">
+        <v>8148</v>
+      </c>
+      <c r="C17" s="7">
+        <v>2044</v>
+      </c>
+      <c r="D17" s="7">
+        <v>24674</v>
+      </c>
+      <c r="E17" s="7">
+        <v>3553</v>
+      </c>
+      <c r="F17" s="8">
+        <v>5447</v>
+      </c>
+      <c r="G17" s="7">
+        <v>393</v>
+      </c>
+      <c r="H17" s="7">
+        <v>2585</v>
+      </c>
+      <c r="I17" s="7">
+        <v>809</v>
+      </c>
+      <c r="J17" s="7">
+        <v>1481</v>
+      </c>
+      <c r="K17" s="7">
+        <v>1076</v>
+      </c>
+      <c r="L17" s="7">
+        <v>1196</v>
+      </c>
+      <c r="M17" s="7">
+        <v>1907</v>
+      </c>
+      <c r="N17" s="7">
+        <v>597</v>
+      </c>
+      <c r="O17" s="7">
+        <v>14637</v>
+      </c>
+      <c r="P17" s="7">
+        <v>591</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>389</v>
+      </c>
+      <c r="R17" s="7">
+        <v>664</v>
+      </c>
+      <c r="S17" s="7">
+        <v>4427</v>
+      </c>
+      <c r="T17" s="8">
+        <v>1346</v>
+      </c>
+      <c r="U17" s="7">
+        <v>2705</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <f t="shared" si="0"/>
+        <v>1916</v>
+      </c>
+      <c r="B18" s="7">
+        <v>8303</v>
+      </c>
+      <c r="C18" s="7">
+        <v>2062</v>
+      </c>
+      <c r="D18" s="7">
+        <v>25197</v>
+      </c>
+      <c r="E18" s="7">
+        <v>3598</v>
+      </c>
+      <c r="F18" s="8">
+        <v>5579</v>
+      </c>
+      <c r="G18" s="7">
+        <v>398</v>
+      </c>
+      <c r="H18" s="7">
+        <v>2664</v>
+      </c>
+      <c r="I18" s="7">
+        <v>823</v>
+      </c>
+      <c r="J18" s="7">
+        <v>1493</v>
+      </c>
+      <c r="K18" s="7">
+        <v>1095</v>
+      </c>
+      <c r="L18" s="7">
+        <v>1211</v>
+      </c>
+      <c r="M18" s="7">
+        <v>1949</v>
+      </c>
+      <c r="N18" s="7">
+        <v>606</v>
+      </c>
+      <c r="O18" s="7">
+        <v>14029</v>
+      </c>
+      <c r="P18" s="7">
+        <v>600</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>401</v>
+      </c>
+      <c r="R18" s="7">
+        <v>671</v>
+      </c>
+      <c r="S18" s="7">
+        <v>4508</v>
+      </c>
+      <c r="T18" s="8">
+        <v>1379</v>
+      </c>
+      <c r="U18" s="7">
+        <v>2727</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <f t="shared" si="0"/>
+        <v>1917</v>
+      </c>
+      <c r="B19" s="7">
+        <v>8445</v>
+      </c>
+      <c r="C19" s="7">
+        <v>2081</v>
+      </c>
+      <c r="D19" s="7">
+        <v>25732</v>
+      </c>
+      <c r="E19" s="7">
+        <v>3644</v>
+      </c>
+      <c r="F19" s="8">
+        <v>5715</v>
+      </c>
+      <c r="G19" s="7">
+        <v>404</v>
+      </c>
+      <c r="H19" s="7">
+        <v>2746</v>
+      </c>
+      <c r="I19" s="7">
+        <v>837</v>
+      </c>
+      <c r="J19" s="7">
+        <v>1505</v>
+      </c>
+      <c r="K19" s="7">
+        <v>1113</v>
+      </c>
+      <c r="L19" s="7">
+        <v>1226</v>
+      </c>
+      <c r="M19" s="7">
+        <v>1993</v>
+      </c>
+      <c r="N19" s="7">
+        <v>633</v>
+      </c>
+      <c r="O19" s="7">
+        <v>13898</v>
+      </c>
+      <c r="P19" s="7">
+        <v>610</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>413</v>
+      </c>
+      <c r="R19" s="7">
+        <v>678</v>
+      </c>
+      <c r="S19" s="7">
+        <v>4588</v>
+      </c>
+      <c r="T19" s="8">
+        <v>1407</v>
+      </c>
+      <c r="U19" s="7">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <f t="shared" si="0"/>
+        <v>1918</v>
+      </c>
+      <c r="B20" s="7">
+        <v>8590</v>
+      </c>
+      <c r="C20" s="7">
+        <v>2099</v>
+      </c>
+      <c r="D20" s="7">
+        <v>26277</v>
+      </c>
+      <c r="E20" s="7">
+        <v>3690</v>
+      </c>
+      <c r="F20" s="8">
+        <v>5855</v>
+      </c>
+      <c r="G20" s="7">
+        <v>410</v>
+      </c>
+      <c r="H20" s="7">
+        <v>2828</v>
+      </c>
+      <c r="I20" s="7">
+        <v>851</v>
+      </c>
+      <c r="J20" s="7">
+        <v>1517</v>
+      </c>
+      <c r="K20" s="7">
+        <v>1131</v>
+      </c>
+      <c r="L20" s="7">
+        <v>1241</v>
+      </c>
+      <c r="M20" s="7">
+        <v>2037</v>
+      </c>
+      <c r="N20" s="7">
+        <v>660</v>
+      </c>
+      <c r="O20" s="7">
+        <v>14000</v>
+      </c>
+      <c r="P20" s="7">
+        <v>619</v>
+      </c>
+      <c r="Q20" s="7">
+        <v>426</v>
+      </c>
+      <c r="R20" s="7">
+        <v>685</v>
+      </c>
+      <c r="S20" s="7">
+        <v>4668</v>
+      </c>
+      <c r="T20" s="8">
+        <v>1430</v>
+      </c>
+      <c r="U20" s="7">
+        <v>2772</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <f t="shared" si="0"/>
+        <v>1919</v>
+      </c>
+      <c r="B21" s="7">
+        <v>8754</v>
+      </c>
+      <c r="C21" s="7">
+        <v>2118</v>
+      </c>
+      <c r="D21" s="7">
+        <v>26835</v>
+      </c>
+      <c r="E21" s="7">
+        <v>3737</v>
+      </c>
+      <c r="F21" s="8">
+        <v>6029</v>
+      </c>
+      <c r="G21" s="7">
+        <v>415</v>
+      </c>
+      <c r="H21" s="7">
+        <v>2912</v>
+      </c>
+      <c r="I21" s="7">
+        <v>865</v>
+      </c>
+      <c r="J21" s="7">
+        <v>1529</v>
+      </c>
+      <c r="K21" s="7">
+        <v>1150</v>
+      </c>
+      <c r="L21" s="7">
+        <v>1257</v>
+      </c>
+      <c r="M21" s="7">
+        <v>2080</v>
+      </c>
+      <c r="N21" s="7">
+        <v>688</v>
+      </c>
+      <c r="O21" s="7">
+        <v>14150</v>
+      </c>
+      <c r="P21" s="7">
+        <v>629</v>
+      </c>
+      <c r="Q21" s="7">
+        <v>437</v>
+      </c>
+      <c r="R21" s="7">
+        <v>692</v>
+      </c>
+      <c r="S21" s="7">
+        <v>4748</v>
+      </c>
+      <c r="T21" s="8">
+        <v>1463</v>
+      </c>
+      <c r="U21" s="7">
+        <v>2795</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <f t="shared" si="0"/>
+        <v>1920</v>
+      </c>
+      <c r="B22" s="7">
+        <v>8969</v>
+      </c>
+      <c r="C22" s="7">
+        <v>2136</v>
+      </c>
+      <c r="D22" s="7">
+        <v>27404</v>
+      </c>
+      <c r="E22" s="7">
+        <v>3785</v>
+      </c>
+      <c r="F22" s="8">
+        <v>6089</v>
+      </c>
+      <c r="G22" s="7">
+        <v>421</v>
+      </c>
+      <c r="H22" s="7">
+        <v>2997</v>
+      </c>
+      <c r="I22" s="7">
+        <v>879</v>
+      </c>
+      <c r="J22" s="7">
+        <v>1541</v>
+      </c>
+      <c r="K22" s="7">
+        <v>1168</v>
+      </c>
+      <c r="L22" s="7">
+        <v>1272</v>
+      </c>
+      <c r="M22" s="7">
+        <v>2124</v>
+      </c>
+      <c r="N22" s="7">
+        <v>715</v>
+      </c>
+      <c r="O22" s="7">
+        <v>14150</v>
+      </c>
+      <c r="P22" s="7">
+        <v>638</v>
+      </c>
+      <c r="Q22" s="7">
+        <v>447</v>
+      </c>
+      <c r="R22" s="7">
+        <v>699</v>
+      </c>
+      <c r="S22" s="7">
+        <v>4828</v>
+      </c>
+      <c r="T22" s="8">
+        <v>1481</v>
+      </c>
+      <c r="U22" s="7">
+        <v>2818</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <f t="shared" si="0"/>
+        <v>1921</v>
+      </c>
+      <c r="B23" s="7">
+        <v>9215</v>
+      </c>
+      <c r="C23" s="7">
+        <v>2161</v>
+      </c>
+      <c r="D23" s="7">
+        <v>27969</v>
+      </c>
+      <c r="E23" s="7">
+        <v>3853</v>
+      </c>
+      <c r="F23" s="8">
+        <v>6211</v>
+      </c>
+      <c r="G23" s="7">
+        <v>425</v>
+      </c>
+      <c r="H23" s="7">
+        <v>3083</v>
+      </c>
+      <c r="I23" s="7">
+        <v>912</v>
+      </c>
+      <c r="J23" s="7">
+        <v>1570</v>
+      </c>
+      <c r="K23" s="7">
+        <v>1193</v>
+      </c>
+      <c r="L23" s="7">
+        <v>1319</v>
+      </c>
+      <c r="M23" s="7">
+        <v>2151</v>
+      </c>
+      <c r="N23" s="7">
+        <v>742</v>
+      </c>
+      <c r="O23" s="7">
+        <v>14335</v>
+      </c>
+      <c r="P23" s="7">
+        <v>643</v>
+      </c>
+      <c r="Q23" s="7">
+        <v>449</v>
+      </c>
+      <c r="R23" s="7">
+        <v>715</v>
+      </c>
+      <c r="S23" s="7">
+        <v>4908</v>
+      </c>
+      <c r="T23" s="8">
+        <v>1499</v>
+      </c>
+      <c r="U23" s="7">
+        <v>2843</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <f t="shared" si="0"/>
+        <v>1922</v>
+      </c>
+      <c r="B24" s="7">
+        <v>9521</v>
+      </c>
+      <c r="C24" s="7">
+        <v>2186</v>
+      </c>
+      <c r="D24" s="7">
+        <v>28542</v>
+      </c>
+      <c r="E24" s="7">
+        <v>3907</v>
+      </c>
+      <c r="F24" s="8">
+        <v>6336</v>
+      </c>
+      <c r="G24" s="7">
+        <v>431</v>
+      </c>
+      <c r="H24" s="7">
+        <v>3170</v>
+      </c>
+      <c r="I24" s="7">
+        <v>946</v>
+      </c>
+      <c r="J24" s="7">
+        <v>1610</v>
+      </c>
+      <c r="K24" s="7">
+        <v>1217</v>
+      </c>
+      <c r="L24" s="7">
+        <v>1367</v>
+      </c>
+      <c r="M24" s="7">
+        <v>2178</v>
+      </c>
+      <c r="N24" s="7">
+        <v>769</v>
+      </c>
+      <c r="O24" s="7">
+        <v>14444</v>
+      </c>
+      <c r="P24" s="7">
+        <v>647</v>
+      </c>
+      <c r="Q24" s="7">
+        <v>451</v>
+      </c>
+      <c r="R24" s="7">
+        <v>732</v>
+      </c>
+      <c r="S24" s="7">
+        <v>4989</v>
+      </c>
+      <c r="T24" s="8">
+        <v>1517</v>
+      </c>
+      <c r="U24" s="7">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <f t="shared" si="0"/>
+        <v>1923</v>
+      </c>
+      <c r="B25" s="7">
+        <v>9892</v>
+      </c>
+      <c r="C25" s="7">
+        <v>2212</v>
+      </c>
+      <c r="D25" s="7">
+        <v>29126</v>
+      </c>
+      <c r="E25" s="7">
+        <v>3961</v>
+      </c>
+      <c r="F25" s="8">
+        <v>6463</v>
+      </c>
+      <c r="G25" s="7">
+        <v>439</v>
+      </c>
+      <c r="H25" s="7">
+        <v>3257</v>
+      </c>
+      <c r="I25" s="7">
+        <v>981</v>
+      </c>
+      <c r="J25" s="7">
+        <v>1646</v>
+      </c>
+      <c r="K25" s="7">
+        <v>1244</v>
+      </c>
+      <c r="L25" s="7">
+        <v>1416</v>
+      </c>
+      <c r="M25" s="7">
+        <v>2206</v>
+      </c>
+      <c r="N25" s="7">
+        <v>796</v>
+      </c>
+      <c r="O25" s="7">
+        <v>14693</v>
+      </c>
+      <c r="P25" s="7">
+        <v>652</v>
+      </c>
+      <c r="Q25" s="7">
+        <v>453</v>
+      </c>
+      <c r="R25" s="7">
+        <v>749</v>
+      </c>
+      <c r="S25" s="7">
+        <v>5069</v>
+      </c>
+      <c r="T25" s="8">
+        <v>1535</v>
+      </c>
+      <c r="U25" s="7">
+        <v>2898</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <f t="shared" si="0"/>
+        <v>1924</v>
+      </c>
+      <c r="B26" s="7">
+        <v>10216</v>
+      </c>
+      <c r="C26" s="7">
+        <v>2237</v>
+      </c>
+      <c r="D26" s="7">
+        <v>29723</v>
+      </c>
+      <c r="E26" s="7">
+        <v>4017</v>
+      </c>
+      <c r="F26" s="8">
+        <v>6592</v>
+      </c>
+      <c r="G26" s="7">
+        <v>447</v>
+      </c>
+      <c r="H26" s="7">
+        <v>3345</v>
+      </c>
+      <c r="I26" s="7">
+        <v>1017</v>
+      </c>
+      <c r="J26" s="7">
+        <v>1685</v>
+      </c>
+      <c r="K26" s="7">
+        <v>1274</v>
+      </c>
+      <c r="L26" s="7">
+        <v>1471</v>
+      </c>
+      <c r="M26" s="7">
+        <v>2232</v>
+      </c>
+      <c r="N26" s="7">
+        <v>824</v>
+      </c>
+      <c r="O26" s="7">
+        <v>14945</v>
+      </c>
+      <c r="P26" s="7">
+        <v>656</v>
+      </c>
+      <c r="Q26" s="7">
+        <v>455</v>
+      </c>
+      <c r="R26" s="7">
+        <v>767</v>
+      </c>
+      <c r="S26" s="7">
+        <v>5148</v>
+      </c>
+      <c r="T26" s="8">
+        <v>1553</v>
+      </c>
+      <c r="U26" s="7">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <f t="shared" si="0"/>
+        <v>1925</v>
+      </c>
+      <c r="B27" s="7">
+        <v>10500</v>
+      </c>
+      <c r="C27" s="7">
+        <v>2263</v>
+      </c>
+      <c r="D27" s="7">
+        <v>30332</v>
+      </c>
+      <c r="E27" s="7">
+        <v>4073</v>
+      </c>
+      <c r="F27" s="7">
+        <v>6724</v>
+      </c>
+      <c r="G27" s="7">
+        <v>456</v>
+      </c>
+      <c r="H27" s="7">
+        <v>3432</v>
+      </c>
+      <c r="I27" s="7">
+        <v>1054</v>
+      </c>
+      <c r="J27" s="7">
+        <v>1724</v>
+      </c>
+      <c r="K27" s="7">
+        <v>1301</v>
+      </c>
+      <c r="L27" s="7">
+        <v>1514</v>
+      </c>
+      <c r="M27" s="7">
+        <v>2260</v>
+      </c>
+      <c r="N27" s="7">
+        <v>851</v>
+      </c>
+      <c r="O27" s="7">
+        <v>15204</v>
+      </c>
+      <c r="P27" s="7">
+        <v>660</v>
+      </c>
+      <c r="Q27" s="7">
+        <v>457</v>
+      </c>
+      <c r="R27" s="7">
+        <v>785</v>
+      </c>
+      <c r="S27" s="7">
+        <v>5229</v>
+      </c>
+      <c r="T27" s="8">
+        <v>1571</v>
+      </c>
+      <c r="U27" s="7">
+        <v>2953</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <f t="shared" si="0"/>
+        <v>1926</v>
+      </c>
+      <c r="B28" s="7">
+        <v>10804</v>
+      </c>
+      <c r="C28" s="7">
+        <v>2289</v>
+      </c>
+      <c r="D28" s="7">
+        <v>30953</v>
+      </c>
+      <c r="E28" s="7">
+        <v>4130</v>
+      </c>
+      <c r="F28" s="7">
+        <v>6859</v>
+      </c>
+      <c r="G28" s="7">
+        <v>466</v>
+      </c>
+      <c r="H28" s="7">
+        <v>3519</v>
+      </c>
+      <c r="I28" s="7">
+        <v>1092</v>
+      </c>
+      <c r="J28" s="7">
+        <v>1762</v>
+      </c>
+      <c r="K28" s="7">
+        <v>1325</v>
+      </c>
+      <c r="L28" s="7">
+        <v>1557</v>
+      </c>
+      <c r="M28" s="7">
+        <v>2292</v>
+      </c>
+      <c r="N28" s="7">
+        <v>878</v>
+      </c>
+      <c r="O28" s="7">
+        <v>15468</v>
+      </c>
+      <c r="P28" s="7">
+        <v>665</v>
+      </c>
+      <c r="Q28" s="7">
+        <v>459</v>
+      </c>
+      <c r="R28" s="7">
+        <v>803</v>
+      </c>
+      <c r="S28" s="7">
+        <v>5313</v>
+      </c>
+      <c r="T28" s="8">
+        <v>1604</v>
+      </c>
+      <c r="U28" s="7">
+        <v>2981</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <f t="shared" si="0"/>
+        <v>1927</v>
+      </c>
+      <c r="B29" s="7">
+        <v>11126</v>
+      </c>
+      <c r="C29" s="7">
+        <v>2316</v>
+      </c>
+      <c r="D29" s="7">
+        <v>31587</v>
+      </c>
+      <c r="E29" s="7">
+        <v>4188</v>
+      </c>
+      <c r="F29" s="7">
+        <v>6996</v>
+      </c>
+      <c r="G29" s="7">
+        <v>472</v>
+      </c>
+      <c r="H29" s="7">
+        <v>3606</v>
+      </c>
+      <c r="I29" s="7">
+        <v>1131</v>
+      </c>
+      <c r="J29" s="7">
+        <v>1800</v>
+      </c>
+      <c r="K29" s="7">
+        <v>1351</v>
+      </c>
+      <c r="L29" s="7">
+        <v>1602</v>
+      </c>
+      <c r="M29" s="7">
+        <v>2325</v>
+      </c>
+      <c r="N29" s="7">
+        <v>893</v>
+      </c>
+      <c r="O29" s="7">
+        <v>15738</v>
+      </c>
+      <c r="P29" s="7">
+        <v>670</v>
+      </c>
+      <c r="Q29" s="7">
+        <v>462</v>
+      </c>
+      <c r="R29" s="7">
+        <v>822</v>
+      </c>
+      <c r="S29" s="7">
+        <v>5399</v>
+      </c>
+      <c r="T29" s="8">
+        <v>1636</v>
+      </c>
+      <c r="U29" s="7">
+        <v>3012</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <f t="shared" si="0"/>
+        <v>1928</v>
+      </c>
+      <c r="B30" s="7">
+        <v>11438</v>
+      </c>
+      <c r="C30" s="7">
+        <v>2343</v>
+      </c>
+      <c r="D30" s="7">
+        <v>32234</v>
+      </c>
+      <c r="E30" s="7">
+        <v>4246</v>
+      </c>
+      <c r="F30" s="7">
+        <v>7136</v>
+      </c>
+      <c r="G30" s="7">
+        <v>479</v>
+      </c>
+      <c r="H30" s="7">
+        <v>3507</v>
+      </c>
+      <c r="I30" s="7">
+        <v>1172</v>
+      </c>
+      <c r="J30" s="7">
+        <v>1846</v>
+      </c>
+      <c r="K30" s="7">
+        <v>1385</v>
+      </c>
+      <c r="L30" s="7">
+        <v>1660</v>
+      </c>
+      <c r="M30" s="7">
+        <v>2357</v>
+      </c>
+      <c r="N30" s="7">
+        <v>911</v>
+      </c>
+      <c r="O30" s="7">
+        <v>16012</v>
+      </c>
+      <c r="P30" s="7">
+        <v>674</v>
+      </c>
+      <c r="Q30" s="7">
+        <v>464</v>
+      </c>
+      <c r="R30" s="7">
+        <v>841</v>
+      </c>
+      <c r="S30" s="7">
+        <v>5482</v>
+      </c>
+      <c r="T30" s="8">
+        <v>1669</v>
+      </c>
+      <c r="U30" s="7">
+        <v>3047</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <f t="shared" si="0"/>
+        <v>1929</v>
+      </c>
+      <c r="B31" s="7">
+        <v>11746</v>
+      </c>
+      <c r="C31" s="7">
+        <v>2370</v>
+      </c>
+      <c r="D31" s="7">
+        <v>32894</v>
+      </c>
+      <c r="E31" s="7">
+        <v>4305</v>
+      </c>
+      <c r="F31" s="7">
+        <v>7279</v>
+      </c>
+      <c r="G31" s="7">
+        <v>489</v>
+      </c>
+      <c r="H31" s="7">
+        <v>3577</v>
+      </c>
+      <c r="I31" s="7">
+        <v>1213</v>
+      </c>
+      <c r="J31" s="7">
+        <v>1891</v>
+      </c>
+      <c r="K31" s="7">
+        <v>1412</v>
+      </c>
+      <c r="L31" s="7">
+        <v>1706</v>
+      </c>
+      <c r="M31" s="7">
+        <v>2390</v>
+      </c>
+      <c r="N31" s="7">
+        <v>928</v>
+      </c>
+      <c r="O31" s="7">
+        <v>16926</v>
+      </c>
+      <c r="P31" s="7">
+        <v>679</v>
+      </c>
+      <c r="Q31" s="7">
+        <v>466</v>
+      </c>
+      <c r="R31" s="7">
+        <v>860</v>
+      </c>
+      <c r="S31" s="7">
+        <v>5567</v>
+      </c>
+      <c r="T31" s="8">
+        <v>1701</v>
+      </c>
+      <c r="U31" s="7">
+        <v>3082</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <f t="shared" si="0"/>
+        <v>1930</v>
+      </c>
+      <c r="B32" s="7">
+        <v>12047</v>
+      </c>
+      <c r="C32" s="7">
+        <v>2397</v>
+      </c>
+      <c r="D32" s="7">
+        <v>33568</v>
+      </c>
+      <c r="E32" s="7">
+        <v>4365</v>
+      </c>
+      <c r="F32" s="7">
+        <v>7425</v>
+      </c>
+      <c r="G32" s="7">
+        <v>499</v>
+      </c>
+      <c r="H32" s="7">
+        <v>3647</v>
+      </c>
+      <c r="I32" s="7">
+        <v>1256</v>
+      </c>
+      <c r="J32" s="7">
+        <v>1944</v>
+      </c>
+      <c r="K32" s="7">
+        <v>1443</v>
+      </c>
+      <c r="L32" s="7">
+        <v>1755</v>
+      </c>
+      <c r="M32" s="7">
+        <v>2422</v>
+      </c>
+      <c r="N32" s="7">
+        <v>948</v>
+      </c>
+      <c r="O32" s="7">
+        <v>16553</v>
+      </c>
+      <c r="P32" s="7">
+        <v>683</v>
+      </c>
+      <c r="Q32" s="7">
+        <v>471</v>
+      </c>
+      <c r="R32" s="7">
+        <v>880</v>
+      </c>
+      <c r="S32" s="7">
+        <v>5651</v>
+      </c>
+      <c r="T32" s="8">
+        <v>1734</v>
+      </c>
+      <c r="U32" s="7">
+        <v>3118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <f t="shared" si="0"/>
+        <v>1931</v>
+      </c>
+      <c r="B33" s="7">
+        <v>12287</v>
+      </c>
+      <c r="C33" s="7">
+        <v>2425</v>
+      </c>
+      <c r="D33" s="7">
+        <v>34256</v>
+      </c>
+      <c r="E33" s="7">
+        <v>4429</v>
+      </c>
+      <c r="F33" s="7">
+        <v>7574</v>
+      </c>
+      <c r="G33" s="7">
+        <v>508</v>
+      </c>
+      <c r="H33" s="7">
+        <v>3962</v>
+      </c>
+      <c r="I33" s="7">
+        <v>1300</v>
+      </c>
+      <c r="J33" s="7">
+        <v>1995</v>
+      </c>
+      <c r="K33" s="7">
+        <v>1456</v>
+      </c>
+      <c r="L33" s="7">
+        <v>1813</v>
+      </c>
+      <c r="M33" s="7">
+        <v>2460</v>
+      </c>
+      <c r="N33" s="7">
+        <v>968</v>
+      </c>
+      <c r="O33" s="7">
+        <v>16876</v>
+      </c>
+      <c r="P33" s="7">
+        <v>687</v>
+      </c>
+      <c r="Q33" s="7">
+        <v>486</v>
+      </c>
+      <c r="R33" s="7">
+        <v>901</v>
+      </c>
+      <c r="S33" s="7">
+        <v>5748</v>
+      </c>
+      <c r="T33" s="8">
+        <v>1761</v>
+      </c>
+      <c r="U33" s="7">
+        <v>3154</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <f t="shared" si="0"/>
+        <v>1932</v>
+      </c>
+      <c r="B34" s="7">
+        <v>12517</v>
+      </c>
+      <c r="C34" s="7">
+        <v>2453</v>
+      </c>
+      <c r="D34" s="7">
+        <v>34957</v>
+      </c>
+      <c r="E34" s="7">
+        <v>4495</v>
+      </c>
+      <c r="F34" s="7">
+        <v>7726</v>
+      </c>
+      <c r="G34" s="7">
+        <v>518</v>
+      </c>
+      <c r="H34" s="7">
+        <v>3962</v>
+      </c>
+      <c r="I34" s="7">
+        <v>1345</v>
+      </c>
+      <c r="J34" s="7">
+        <v>2050</v>
+      </c>
+      <c r="K34" s="7">
+        <v>1474</v>
+      </c>
+      <c r="L34" s="7">
+        <v>1864</v>
+      </c>
+      <c r="M34" s="7">
+        <v>2498</v>
+      </c>
+      <c r="N34" s="7">
+        <v>989</v>
+      </c>
+      <c r="O34" s="7">
+        <v>17170</v>
+      </c>
+      <c r="P34" s="7">
+        <v>692</v>
+      </c>
+      <c r="Q34" s="7">
+        <v>501</v>
+      </c>
+      <c r="R34" s="7">
+        <v>922</v>
+      </c>
+      <c r="S34" s="7">
+        <v>5844</v>
+      </c>
+      <c r="T34" s="8">
+        <v>1788</v>
+      </c>
+      <c r="U34" s="7">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <f t="shared" si="0"/>
+        <v>1933</v>
+      </c>
+      <c r="B35" s="7">
+        <v>12729</v>
+      </c>
+      <c r="C35" s="7">
+        <v>2482</v>
+      </c>
+      <c r="D35" s="7">
+        <v>35673</v>
+      </c>
+      <c r="E35" s="7">
+        <v>4563</v>
+      </c>
+      <c r="F35" s="7">
+        <v>7880</v>
+      </c>
+      <c r="G35" s="7">
+        <v>528</v>
+      </c>
+      <c r="H35" s="7">
+        <v>3962</v>
+      </c>
+      <c r="I35" s="7">
+        <v>1391</v>
+      </c>
+      <c r="J35" s="7">
+        <v>2095</v>
+      </c>
+      <c r="K35" s="7">
+        <v>1493</v>
+      </c>
+      <c r="L35" s="7">
+        <v>1909</v>
+      </c>
+      <c r="M35" s="7">
+        <v>2535</v>
+      </c>
+      <c r="N35" s="7">
+        <v>1007</v>
+      </c>
+      <c r="O35" s="7">
+        <v>17470</v>
+      </c>
+      <c r="P35" s="7">
+        <v>697</v>
+      </c>
+      <c r="Q35" s="7">
+        <v>516</v>
+      </c>
+      <c r="R35" s="7">
+        <v>944</v>
+      </c>
+      <c r="S35" s="7">
+        <v>5941</v>
+      </c>
+      <c r="T35" s="8">
+        <v>1815</v>
+      </c>
+      <c r="U35" s="7">
+        <v>3227</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <f t="shared" si="0"/>
+        <v>1934</v>
+      </c>
+      <c r="B36" s="7">
+        <v>12940</v>
+      </c>
+      <c r="C36" s="7">
+        <v>2511</v>
+      </c>
+      <c r="D36" s="7">
+        <v>36404</v>
+      </c>
+      <c r="E36" s="7">
+        <v>4631</v>
+      </c>
+      <c r="F36" s="7">
+        <v>8038</v>
+      </c>
+      <c r="G36" s="7">
+        <v>540</v>
+      </c>
+      <c r="H36" s="7">
+        <v>4039</v>
+      </c>
+      <c r="I36" s="7">
+        <v>1438</v>
+      </c>
+      <c r="J36" s="7">
+        <v>2140</v>
+      </c>
+      <c r="K36" s="7">
+        <v>1512</v>
+      </c>
+      <c r="L36" s="7">
+        <v>1943</v>
+      </c>
+      <c r="M36" s="7">
+        <v>2573</v>
+      </c>
+      <c r="N36" s="7">
+        <v>1023</v>
+      </c>
+      <c r="O36" s="7">
+        <v>17777</v>
+      </c>
+      <c r="P36" s="7">
+        <v>711</v>
+      </c>
+      <c r="Q36" s="7">
+        <v>531</v>
+      </c>
+      <c r="R36" s="7">
+        <v>966</v>
+      </c>
+      <c r="S36" s="7">
+        <v>6037</v>
+      </c>
+      <c r="T36" s="8">
+        <v>1842</v>
+      </c>
+      <c r="U36" s="7">
+        <v>3264</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <f t="shared" si="0"/>
+        <v>1935</v>
+      </c>
+      <c r="B37" s="7">
+        <v>13148</v>
+      </c>
+      <c r="C37" s="7">
+        <v>2540</v>
+      </c>
+      <c r="D37" s="7">
+        <v>37150</v>
+      </c>
+      <c r="E37" s="7">
+        <v>4700</v>
+      </c>
+      <c r="F37" s="7">
+        <v>8199</v>
+      </c>
+      <c r="G37" s="7">
+        <v>551</v>
+      </c>
+      <c r="H37" s="7">
+        <v>4071</v>
+      </c>
+      <c r="I37" s="7">
+        <v>1484</v>
+      </c>
+      <c r="J37" s="7">
+        <v>2196</v>
+      </c>
+      <c r="K37" s="7">
+        <v>1531</v>
+      </c>
+      <c r="L37" s="7">
+        <v>1975</v>
+      </c>
+      <c r="M37" s="7">
+        <v>2611</v>
+      </c>
+      <c r="N37" s="7">
+        <v>1042</v>
+      </c>
+      <c r="O37" s="7">
+        <v>18089</v>
+      </c>
+      <c r="P37" s="7">
+        <v>728</v>
+      </c>
+      <c r="Q37" s="7">
+        <v>546</v>
+      </c>
+      <c r="R37" s="7">
+        <v>988</v>
+      </c>
+      <c r="S37" s="7">
+        <v>6134</v>
+      </c>
+      <c r="T37" s="8">
+        <v>1869</v>
+      </c>
+      <c r="U37" s="7">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <f t="shared" si="0"/>
+        <v>1936</v>
+      </c>
+      <c r="B38" s="7">
+        <v>13372</v>
+      </c>
+      <c r="C38" s="7">
+        <v>2569</v>
+      </c>
+      <c r="D38" s="7">
+        <v>37911</v>
+      </c>
+      <c r="E38" s="7">
+        <v>4771</v>
+      </c>
+      <c r="F38" s="7">
+        <v>8363</v>
+      </c>
+      <c r="G38" s="7">
+        <v>563</v>
+      </c>
+      <c r="H38" s="7">
+        <v>4109</v>
+      </c>
+      <c r="I38" s="7">
+        <v>1520</v>
+      </c>
+      <c r="J38" s="7">
+        <v>2249</v>
+      </c>
+      <c r="K38" s="7">
+        <v>1551</v>
+      </c>
+      <c r="L38" s="7">
+        <v>2023</v>
+      </c>
+      <c r="M38" s="7">
+        <v>2654</v>
+      </c>
+      <c r="N38" s="7">
+        <v>1058</v>
+      </c>
+      <c r="O38" s="7">
+        <v>18410</v>
+      </c>
+      <c r="P38" s="7">
+        <v>746</v>
+      </c>
+      <c r="Q38" s="7">
+        <v>561</v>
+      </c>
+      <c r="R38" s="7">
+        <v>1012</v>
+      </c>
+      <c r="S38" s="7">
+        <v>6243</v>
+      </c>
+      <c r="T38" s="8">
+        <v>1890</v>
+      </c>
+      <c r="U38" s="7">
+        <v>3382</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <f t="shared" si="0"/>
+        <v>1937</v>
+      </c>
+      <c r="B39" s="7">
+        <v>13608</v>
+      </c>
+      <c r="C39" s="7">
+        <v>2599</v>
+      </c>
+      <c r="D39" s="7">
+        <v>38687</v>
+      </c>
+      <c r="E39" s="7">
+        <v>4842</v>
+      </c>
+      <c r="F39" s="7">
+        <v>8531</v>
+      </c>
+      <c r="G39" s="7">
+        <v>576</v>
+      </c>
+      <c r="H39" s="7">
+        <v>4165</v>
+      </c>
+      <c r="I39" s="7">
+        <v>1558</v>
+      </c>
+      <c r="J39" s="7">
+        <v>2298</v>
+      </c>
+      <c r="K39" s="7">
+        <v>1571</v>
+      </c>
+      <c r="L39" s="7">
+        <v>2066</v>
+      </c>
+      <c r="M39" s="7">
+        <v>2697</v>
+      </c>
+      <c r="N39" s="7">
+        <v>1076</v>
+      </c>
+      <c r="O39" s="7">
+        <v>18764</v>
+      </c>
+      <c r="P39" s="7">
+        <v>765</v>
+      </c>
+      <c r="Q39" s="7">
+        <v>575</v>
+      </c>
+      <c r="R39" s="7">
+        <v>1036</v>
+      </c>
+      <c r="S39" s="7">
+        <v>6353</v>
+      </c>
+      <c r="T39" s="8">
+        <v>1911</v>
+      </c>
+      <c r="U39" s="7">
+        <v>3464</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <f t="shared" si="0"/>
+        <v>1938</v>
+      </c>
+      <c r="B40" s="7">
+        <v>13841</v>
+      </c>
+      <c r="C40" s="7">
+        <v>2629</v>
+      </c>
+      <c r="D40" s="7">
+        <v>39480</v>
+      </c>
+      <c r="E40" s="7">
+        <v>4914</v>
+      </c>
+      <c r="F40" s="7">
+        <v>8702</v>
+      </c>
+      <c r="G40" s="7">
+        <v>590</v>
+      </c>
+      <c r="H40" s="7">
+        <v>4228</v>
+      </c>
+      <c r="I40" s="7">
+        <v>1596</v>
+      </c>
+      <c r="J40" s="7">
+        <v>2355</v>
+      </c>
+      <c r="K40" s="7">
+        <v>1591</v>
+      </c>
+      <c r="L40" s="7">
+        <v>2113</v>
+      </c>
+      <c r="M40" s="7">
+        <v>2741</v>
+      </c>
+      <c r="N40" s="7">
+        <v>1098</v>
+      </c>
+      <c r="O40" s="7">
+        <v>19071</v>
+      </c>
+      <c r="P40" s="7">
+        <v>785</v>
+      </c>
+      <c r="Q40" s="7">
+        <v>590</v>
+      </c>
+      <c r="R40" s="7">
+        <v>1061</v>
+      </c>
+      <c r="S40" s="7">
+        <v>6462</v>
+      </c>
+      <c r="T40" s="8">
+        <v>1932</v>
+      </c>
+      <c r="U40" s="7">
+        <v>3546</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <f t="shared" si="0"/>
+        <v>1939</v>
+      </c>
+      <c r="B41" s="7">
+        <v>14055</v>
+      </c>
+      <c r="C41" s="7">
+        <v>2659</v>
+      </c>
+      <c r="D41" s="7">
+        <v>40289</v>
+      </c>
+      <c r="E41" s="7">
+        <v>4988</v>
+      </c>
+      <c r="F41" s="7">
+        <v>8896</v>
+      </c>
+      <c r="G41" s="7">
+        <v>605</v>
+      </c>
+      <c r="H41" s="7">
+        <v>4253</v>
+      </c>
+      <c r="I41" s="7">
+        <v>1634</v>
+      </c>
+      <c r="J41" s="7">
+        <v>2412</v>
+      </c>
+      <c r="K41" s="7">
+        <v>1612</v>
+      </c>
+      <c r="L41" s="7">
+        <v>2150</v>
+      </c>
+      <c r="M41" s="7">
+        <v>2784</v>
+      </c>
+      <c r="N41" s="7">
+        <v>1122</v>
+      </c>
+      <c r="O41" s="7">
+        <v>19413</v>
+      </c>
+      <c r="P41" s="7">
+        <v>806</v>
+      </c>
+      <c r="Q41" s="7">
+        <v>605</v>
+      </c>
+      <c r="R41" s="7">
+        <v>1086</v>
+      </c>
+      <c r="S41" s="7">
+        <v>6572</v>
+      </c>
+      <c r="T41" s="8">
+        <v>1953</v>
+      </c>
+      <c r="U41" s="7">
+        <v>3628</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <f t="shared" si="0"/>
+        <v>1940</v>
+      </c>
+      <c r="B42" s="7">
+        <v>14169</v>
+      </c>
+      <c r="C42" s="7">
+        <v>2690</v>
+      </c>
+      <c r="D42" s="7">
+        <v>41114</v>
+      </c>
+      <c r="E42" s="7">
+        <v>5063</v>
+      </c>
+      <c r="F42" s="7">
+        <v>9097</v>
+      </c>
+      <c r="G42" s="7">
+        <v>619</v>
+      </c>
+      <c r="H42" s="7">
+        <v>4291</v>
+      </c>
+      <c r="I42" s="7">
+        <v>1759</v>
+      </c>
+      <c r="J42" s="7">
+        <v>2466</v>
+      </c>
+      <c r="K42" s="7">
+        <v>1633</v>
+      </c>
+      <c r="L42" s="7">
+        <v>2201</v>
+      </c>
+      <c r="M42" s="7">
+        <v>2827</v>
+      </c>
+      <c r="N42" s="7">
+        <v>1146</v>
+      </c>
+      <c r="O42" s="7">
+        <v>19654</v>
+      </c>
+      <c r="P42" s="7">
+        <v>825</v>
+      </c>
+      <c r="Q42" s="7">
+        <v>620</v>
+      </c>
+      <c r="R42" s="7">
+        <v>1111</v>
+      </c>
+      <c r="S42" s="7">
+        <v>6681</v>
+      </c>
+      <c r="T42" s="8">
+        <v>1974</v>
+      </c>
+      <c r="U42" s="7">
+        <v>3710</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <f t="shared" si="0"/>
+        <v>1941</v>
+      </c>
+      <c r="B43" s="7">
+        <v>14401</v>
+      </c>
+      <c r="C43" s="7">
+        <v>2721</v>
+      </c>
+      <c r="D43" s="7">
+        <v>42069</v>
+      </c>
+      <c r="E43" s="7">
+        <v>5149</v>
+      </c>
+      <c r="F43" s="7">
+        <v>9315</v>
+      </c>
+      <c r="G43" s="7">
+        <v>633</v>
+      </c>
+      <c r="H43" s="7">
+        <v>4326</v>
+      </c>
+      <c r="I43" s="7">
+        <v>1801</v>
+      </c>
+      <c r="J43" s="7">
+        <v>2521</v>
+      </c>
+      <c r="K43" s="7">
+        <v>1654</v>
+      </c>
+      <c r="L43" s="7">
+        <v>2252</v>
+      </c>
+      <c r="M43" s="7">
+        <v>2876</v>
+      </c>
+      <c r="N43" s="7">
+        <v>1171</v>
+      </c>
+      <c r="O43" s="7">
+        <v>20208</v>
+      </c>
+      <c r="P43" s="7">
+        <v>844</v>
+      </c>
+      <c r="Q43" s="7">
+        <v>636</v>
+      </c>
+      <c r="R43" s="7">
+        <v>1137</v>
+      </c>
+      <c r="S43" s="7">
+        <v>6797</v>
+      </c>
+      <c r="T43" s="8">
+        <v>1994</v>
+      </c>
+      <c r="U43" s="7">
+        <v>3803</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <f t="shared" si="0"/>
+        <v>1942</v>
+      </c>
+      <c r="B44" s="7">
+        <v>14637</v>
+      </c>
+      <c r="C44" s="7">
+        <v>2753</v>
+      </c>
+      <c r="D44" s="7">
+        <v>43062</v>
+      </c>
+      <c r="E44" s="7">
+        <v>5244</v>
+      </c>
+      <c r="F44" s="7">
+        <v>9540</v>
+      </c>
+      <c r="G44" s="7">
+        <v>647</v>
+      </c>
+      <c r="H44" s="7">
+        <v>4372</v>
+      </c>
+      <c r="I44" s="7">
+        <v>1844</v>
+      </c>
+      <c r="J44" s="7">
+        <v>2575</v>
+      </c>
+      <c r="K44" s="7">
+        <v>1675</v>
+      </c>
+      <c r="L44" s="7">
+        <v>2300</v>
+      </c>
+      <c r="M44" s="7">
+        <v>2936</v>
+      </c>
+      <c r="N44" s="7">
+        <v>1195</v>
+      </c>
+      <c r="O44" s="7">
+        <v>20657</v>
+      </c>
+      <c r="P44" s="7">
+        <v>863</v>
+      </c>
+      <c r="Q44" s="7">
+        <v>651</v>
+      </c>
+      <c r="R44" s="7">
+        <v>1164</v>
+      </c>
+      <c r="S44" s="7">
+        <v>6915</v>
+      </c>
+      <c r="T44" s="8">
+        <v>2014</v>
+      </c>
+      <c r="U44" s="7">
+        <v>3914</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <f t="shared" si="0"/>
+        <v>1943</v>
+      </c>
+      <c r="B45" s="7">
+        <v>14877</v>
+      </c>
+      <c r="C45" s="7">
+        <v>2785</v>
+      </c>
+      <c r="D45" s="7">
+        <v>43992</v>
+      </c>
+      <c r="E45" s="7">
+        <v>5341</v>
+      </c>
+      <c r="F45" s="7">
+        <v>9774</v>
+      </c>
+      <c r="G45" s="7">
+        <v>661</v>
+      </c>
+      <c r="H45" s="7">
+        <v>4779</v>
+      </c>
+      <c r="I45" s="7">
+        <v>1889</v>
+      </c>
+      <c r="J45" s="7">
+        <v>2641</v>
+      </c>
+      <c r="K45" s="7">
+        <v>1691</v>
+      </c>
+      <c r="L45" s="7">
+        <v>2339</v>
+      </c>
+      <c r="M45" s="7">
+        <v>2979</v>
+      </c>
+      <c r="N45" s="7">
+        <v>1213</v>
+      </c>
+      <c r="O45" s="7">
+        <v>21165</v>
+      </c>
+      <c r="P45" s="7">
+        <v>880</v>
+      </c>
+      <c r="Q45" s="7">
+        <v>669</v>
+      </c>
+      <c r="R45" s="7">
+        <v>1191</v>
+      </c>
+      <c r="S45" s="7">
+        <v>7035</v>
+      </c>
+      <c r="T45" s="8">
+        <v>2034</v>
+      </c>
+      <c r="U45" s="7">
+        <v>4028</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <f t="shared" si="0"/>
+        <v>1944</v>
+      </c>
+      <c r="B46" s="7">
+        <v>15130</v>
+      </c>
+      <c r="C46" s="7">
+        <v>2817</v>
+      </c>
+      <c r="D46" s="7">
+        <v>44842</v>
+      </c>
+      <c r="E46" s="7">
+        <v>5440</v>
+      </c>
+      <c r="F46" s="7">
+        <v>10016</v>
+      </c>
+      <c r="G46" s="7">
+        <v>677</v>
+      </c>
+      <c r="H46" s="7">
+        <v>4849</v>
+      </c>
+      <c r="I46" s="7">
+        <v>1934</v>
+      </c>
+      <c r="J46" s="7">
+        <v>2712</v>
+      </c>
+      <c r="K46" s="7">
+        <v>1719</v>
+      </c>
+      <c r="L46" s="7">
+        <v>2384</v>
+      </c>
+      <c r="M46" s="7">
+        <v>3032</v>
+      </c>
+      <c r="N46" s="7">
+        <v>1237</v>
+      </c>
+      <c r="O46" s="7">
+        <v>21674</v>
+      </c>
+      <c r="P46" s="7">
+        <v>900</v>
+      </c>
+      <c r="Q46" s="7">
+        <v>685</v>
+      </c>
+      <c r="R46" s="7">
+        <v>1219</v>
+      </c>
+      <c r="S46" s="7">
+        <v>7159</v>
+      </c>
+      <c r="T46" s="8">
+        <v>2055</v>
+      </c>
+      <c r="U46" s="7">
+        <v>4146</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <f t="shared" si="0"/>
+        <v>1945</v>
+      </c>
+      <c r="B47" s="7">
+        <v>15390</v>
+      </c>
+      <c r="C47" s="7">
+        <v>2850</v>
+      </c>
+      <c r="D47" s="7">
+        <v>45860</v>
+      </c>
+      <c r="E47" s="7">
+        <v>5541</v>
+      </c>
+      <c r="F47" s="7">
+        <v>10267</v>
+      </c>
+      <c r="G47" s="7">
+        <v>695</v>
+      </c>
+      <c r="H47" s="7">
+        <v>4932</v>
+      </c>
+      <c r="I47" s="7">
+        <v>1982</v>
+      </c>
+      <c r="J47" s="7">
+        <v>2781</v>
+      </c>
+      <c r="K47" s="7">
+        <v>1742</v>
+      </c>
+      <c r="L47" s="7">
+        <v>2438</v>
+      </c>
+      <c r="M47" s="7">
+        <v>3087</v>
+      </c>
+      <c r="N47" s="7">
+        <v>1261</v>
+      </c>
+      <c r="O47" s="7">
+        <v>22233</v>
+      </c>
+      <c r="P47" s="7">
+        <v>923</v>
+      </c>
+      <c r="Q47" s="7">
+        <v>703</v>
+      </c>
+      <c r="R47" s="7">
+        <v>1247</v>
+      </c>
+      <c r="S47" s="7">
+        <v>7285</v>
+      </c>
+      <c r="T47" s="8">
+        <v>2076</v>
+      </c>
+      <c r="U47" s="7">
+        <v>4267</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <f t="shared" si="0"/>
+        <v>1946</v>
+      </c>
+      <c r="B48" s="7">
+        <v>15654</v>
+      </c>
+      <c r="C48" s="7">
+        <v>2883</v>
+      </c>
+      <c r="D48" s="7">
+        <v>46975</v>
+      </c>
+      <c r="E48" s="7">
+        <v>5643</v>
+      </c>
+      <c r="F48" s="7">
+        <v>10528</v>
+      </c>
+      <c r="G48" s="7">
+        <v>709</v>
+      </c>
+      <c r="H48" s="7">
+        <v>5039</v>
+      </c>
+      <c r="I48" s="7">
+        <v>2030</v>
+      </c>
+      <c r="J48" s="7">
+        <v>2853</v>
+      </c>
+      <c r="K48" s="7">
+        <v>1764</v>
+      </c>
+      <c r="L48" s="7">
+        <v>2498</v>
+      </c>
+      <c r="M48" s="7">
+        <v>3143</v>
+      </c>
+      <c r="N48" s="7">
+        <v>1287</v>
+      </c>
+      <c r="O48" s="7">
+        <v>22779</v>
+      </c>
+      <c r="P48" s="7">
+        <v>949</v>
+      </c>
+      <c r="Q48" s="7">
+        <v>721</v>
+      </c>
+      <c r="R48" s="7">
+        <v>1275</v>
+      </c>
+      <c r="S48" s="7">
+        <v>7415</v>
+      </c>
+      <c r="T48" s="8">
+        <v>2098</v>
+      </c>
+      <c r="U48" s="7">
+        <v>4391</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <f t="shared" si="0"/>
+        <v>1947</v>
+      </c>
+      <c r="B49" s="7">
+        <v>15928</v>
+      </c>
+      <c r="C49" s="7">
+        <v>2916</v>
+      </c>
+      <c r="D49" s="7">
+        <v>48161</v>
+      </c>
+      <c r="E49" s="7">
+        <v>5748</v>
+      </c>
+      <c r="F49" s="7">
+        <v>10800</v>
+      </c>
+      <c r="G49" s="7">
+        <v>726</v>
+      </c>
+      <c r="H49" s="7">
+        <v>5152</v>
+      </c>
+      <c r="I49" s="7">
+        <v>2080</v>
+      </c>
+      <c r="J49" s="7">
+        <v>2936</v>
+      </c>
+      <c r="K49" s="7">
+        <v>1788</v>
+      </c>
+      <c r="L49" s="7">
+        <v>2566</v>
+      </c>
+      <c r="M49" s="7">
+        <v>3200</v>
+      </c>
+      <c r="N49" s="7">
+        <v>1320</v>
+      </c>
+      <c r="O49" s="7">
+        <v>23440</v>
+      </c>
+      <c r="P49" s="7">
+        <v>977</v>
+      </c>
+      <c r="Q49" s="7">
+        <v>739</v>
+      </c>
+      <c r="R49" s="7">
+        <v>1305</v>
+      </c>
+      <c r="S49" s="7">
+        <v>7547</v>
+      </c>
+      <c r="T49" s="8">
+        <v>2121</v>
+      </c>
+      <c r="U49" s="7">
+        <v>4548</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <f t="shared" si="0"/>
+        <v>1948</v>
+      </c>
+      <c r="B50" s="7">
+        <v>16269</v>
+      </c>
+      <c r="C50" s="7">
+        <v>2950</v>
+      </c>
+      <c r="D50" s="7">
+        <v>49422</v>
+      </c>
+      <c r="E50" s="7">
+        <v>5854</v>
+      </c>
+      <c r="F50" s="7">
+        <v>11081</v>
+      </c>
+      <c r="G50" s="7">
+        <v>746</v>
+      </c>
+      <c r="H50" s="7">
+        <v>5268</v>
+      </c>
+      <c r="I50" s="7">
+        <v>2131</v>
+      </c>
+      <c r="J50" s="7">
+        <v>3017</v>
+      </c>
+      <c r="K50" s="7">
+        <v>1811</v>
+      </c>
+      <c r="L50" s="7">
+        <v>2641</v>
+      </c>
+      <c r="M50" s="7">
+        <v>3258</v>
+      </c>
+      <c r="N50" s="7">
+        <v>1353</v>
+      </c>
+      <c r="O50" s="7">
+        <v>24129</v>
+      </c>
+      <c r="P50" s="7">
+        <v>1001</v>
+      </c>
+      <c r="Q50" s="7">
+        <v>758</v>
+      </c>
+      <c r="R50" s="7">
+        <v>1335</v>
+      </c>
+      <c r="S50" s="7">
+        <v>7682</v>
+      </c>
+      <c r="T50" s="8">
+        <v>2144</v>
+      </c>
+      <c r="U50" s="7">
+        <v>4686</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <f t="shared" si="0"/>
+        <v>1949</v>
+      </c>
+      <c r="B51" s="7">
+        <v>16656</v>
+      </c>
+      <c r="C51" s="7">
+        <v>2955</v>
+      </c>
+      <c r="D51" s="7">
+        <v>50759</v>
+      </c>
+      <c r="E51" s="7">
+        <v>5962</v>
+      </c>
+      <c r="F51" s="7">
+        <v>11373</v>
+      </c>
+      <c r="G51" s="7">
+        <v>771</v>
+      </c>
+      <c r="H51" s="7">
+        <v>5386</v>
+      </c>
+      <c r="I51" s="7">
+        <v>2185</v>
+      </c>
+      <c r="J51" s="7">
+        <v>3104</v>
+      </c>
+      <c r="K51" s="7">
+        <v>1835</v>
+      </c>
+      <c r="L51" s="7">
+        <v>2724</v>
+      </c>
+      <c r="M51" s="7">
+        <v>3318</v>
+      </c>
+      <c r="N51" s="7">
+        <v>1389</v>
+      </c>
+      <c r="O51" s="7">
+        <v>24825</v>
+      </c>
+      <c r="P51" s="7">
+        <v>1028</v>
+      </c>
+      <c r="Q51" s="7">
+        <v>777</v>
+      </c>
+      <c r="R51" s="7">
+        <v>1366</v>
+      </c>
+      <c r="S51" s="7">
+        <v>7822</v>
+      </c>
+      <c r="T51" s="8">
+        <v>2169</v>
+      </c>
+      <c r="U51" s="7">
+        <v>4828</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <f t="shared" si="0"/>
+        <v>1950</v>
+      </c>
+      <c r="B52" s="7">
+        <v>17070</v>
+      </c>
+      <c r="C52" s="7">
+        <v>3013</v>
+      </c>
+      <c r="D52" s="7">
+        <v>52178</v>
+      </c>
+      <c r="E52" s="7">
+        <v>6073</v>
+      </c>
+      <c r="F52" s="7">
+        <v>11679</v>
+      </c>
+      <c r="G52" s="7">
+        <v>801</v>
+      </c>
+      <c r="H52" s="7">
+        <v>5508</v>
+      </c>
+      <c r="I52" s="7">
+        <v>2243</v>
+      </c>
+      <c r="J52" s="7">
+        <v>3197</v>
+      </c>
+      <c r="K52" s="7">
+        <v>1868</v>
+      </c>
+      <c r="L52" s="7">
+        <v>2805</v>
+      </c>
+      <c r="M52" s="7">
+        <v>3380</v>
+      </c>
+      <c r="N52" s="7">
+        <v>1428</v>
+      </c>
+      <c r="O52" s="7">
+        <v>25791</v>
+      </c>
+      <c r="P52" s="7">
+        <v>1060</v>
+      </c>
+      <c r="Q52" s="7">
+        <v>797</v>
+      </c>
+      <c r="R52" s="7">
+        <v>1397</v>
+      </c>
+      <c r="S52" s="7">
+        <v>7969</v>
+      </c>
+      <c r="T52" s="8">
+        <v>2195</v>
+      </c>
+      <c r="U52" s="7">
+        <v>4974</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <f>A52+1</f>
+        <v>1951</v>
+      </c>
+      <c r="B53" s="7">
+        <v>17481</v>
+      </c>
+      <c r="C53" s="7">
+        <v>3072</v>
+      </c>
+      <c r="D53" s="7">
+        <v>53682</v>
+      </c>
+      <c r="E53" s="7">
+        <v>6211</v>
+      </c>
+      <c r="F53" s="7">
+        <v>12000</v>
+      </c>
+      <c r="G53" s="7">
+        <v>834</v>
+      </c>
+      <c r="H53" s="7">
+        <v>5621</v>
+      </c>
+      <c r="I53" s="7">
+        <v>2305</v>
+      </c>
+      <c r="J53" s="7">
+        <v>3252</v>
+      </c>
+      <c r="K53" s="7">
+        <v>1902</v>
+      </c>
+      <c r="L53" s="7">
+        <v>2892</v>
+      </c>
+      <c r="M53" s="7">
+        <v>3444</v>
+      </c>
+      <c r="N53" s="7">
+        <v>1470</v>
+      </c>
+      <c r="O53" s="7">
+        <v>25585</v>
+      </c>
+      <c r="P53" s="7">
+        <v>1093</v>
+      </c>
+      <c r="Q53" s="7">
+        <v>817</v>
+      </c>
+      <c r="R53" s="7">
+        <v>1429</v>
+      </c>
+      <c r="S53" s="7">
+        <v>8118</v>
+      </c>
+      <c r="T53" s="8">
+        <v>2224</v>
+      </c>
+      <c r="U53" s="7">
+        <v>5139</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <f t="shared" ref="A54:A74" si="1">A53+1</f>
+        <v>1952</v>
+      </c>
+      <c r="B54" s="7">
+        <v>17858</v>
+      </c>
+      <c r="C54" s="7">
+        <v>3132</v>
+      </c>
+      <c r="D54" s="7">
+        <v>55271</v>
+      </c>
+      <c r="E54" s="7">
+        <v>6349</v>
+      </c>
+      <c r="F54" s="7">
+        <v>12339</v>
+      </c>
+      <c r="G54" s="7">
+        <v>869</v>
+      </c>
+      <c r="H54" s="7">
+        <v>5725</v>
+      </c>
+      <c r="I54" s="7">
+        <v>2370</v>
+      </c>
+      <c r="J54" s="7">
+        <v>3350</v>
+      </c>
+      <c r="K54" s="7">
+        <v>1952</v>
+      </c>
+      <c r="L54" s="7">
+        <v>2981</v>
+      </c>
+      <c r="M54" s="7">
+        <v>3510</v>
+      </c>
+      <c r="N54" s="7">
+        <v>1513</v>
+      </c>
+      <c r="O54" s="7">
+        <v>27403</v>
+      </c>
+      <c r="P54" s="7">
+        <v>1128</v>
+      </c>
+      <c r="Q54" s="7">
+        <v>840</v>
+      </c>
+      <c r="R54" s="7">
+        <v>1462</v>
+      </c>
+      <c r="S54" s="7">
+        <v>8267</v>
+      </c>
+      <c r="T54" s="8">
+        <v>2255</v>
+      </c>
+      <c r="U54" s="7">
+        <v>5329</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <f t="shared" si="1"/>
+        <v>1953</v>
+      </c>
+      <c r="B55" s="7">
+        <v>18202</v>
+      </c>
+      <c r="C55" s="7">
+        <v>3193</v>
+      </c>
+      <c r="D55" s="7">
+        <v>56935</v>
+      </c>
+      <c r="E55" s="7">
+        <v>6515</v>
+      </c>
+      <c r="F55" s="7">
+        <v>12693</v>
+      </c>
+      <c r="G55" s="7">
+        <v>906</v>
+      </c>
+      <c r="H55" s="7">
+        <v>5876</v>
+      </c>
+      <c r="I55" s="7">
+        <v>2438</v>
+      </c>
+      <c r="J55" s="7">
+        <v>3464</v>
+      </c>
+      <c r="K55" s="7">
+        <v>2011</v>
+      </c>
+      <c r="L55" s="7">
+        <v>3058</v>
+      </c>
+      <c r="M55" s="7">
+        <v>3577</v>
+      </c>
+      <c r="N55" s="7">
+        <v>1556</v>
+      </c>
+      <c r="O55" s="7">
+        <v>28246</v>
+      </c>
+      <c r="P55" s="7">
+        <v>1165</v>
+      </c>
+      <c r="Q55" s="7">
+        <v>864</v>
+      </c>
+      <c r="R55" s="7">
+        <v>1496</v>
+      </c>
+      <c r="S55" s="7">
+        <v>8425</v>
+      </c>
+      <c r="T55" s="8">
+        <v>2288</v>
+      </c>
+      <c r="U55" s="7">
+        <v>5556</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <f t="shared" si="1"/>
+        <v>1954</v>
+      </c>
+      <c r="B56" s="7">
+        <v>18544</v>
+      </c>
+      <c r="C56" s="7">
+        <v>3256</v>
+      </c>
+      <c r="D56" s="7">
+        <v>58666</v>
+      </c>
+      <c r="E56" s="7">
+        <v>6691</v>
+      </c>
+      <c r="F56" s="7">
+        <v>13062</v>
+      </c>
+      <c r="G56" s="7">
+        <v>944</v>
+      </c>
+      <c r="H56" s="7">
+        <v>6000</v>
+      </c>
+      <c r="I56" s="7">
+        <v>2511</v>
+      </c>
+      <c r="J56" s="7">
+        <v>3567</v>
+      </c>
+      <c r="K56" s="7">
+        <v>2075</v>
+      </c>
+      <c r="L56" s="7">
+        <v>3159</v>
+      </c>
+      <c r="M56" s="7">
+        <v>3648</v>
+      </c>
+      <c r="N56" s="7">
+        <v>1608</v>
+      </c>
+      <c r="O56" s="7">
+        <v>29115</v>
+      </c>
+      <c r="P56" s="7">
+        <v>1203</v>
+      </c>
+      <c r="Q56" s="7">
+        <v>889</v>
+      </c>
+      <c r="R56" s="7">
+        <v>1530</v>
+      </c>
+      <c r="S56" s="7">
+        <v>8597</v>
+      </c>
+      <c r="T56" s="8">
+        <v>2319</v>
+      </c>
+      <c r="U56" s="7">
+        <v>5791</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <f t="shared" si="1"/>
+        <v>1955</v>
+      </c>
+      <c r="B57" s="7">
+        <v>18899</v>
+      </c>
+      <c r="C57" s="7">
+        <v>3322</v>
+      </c>
+      <c r="D57" s="7">
+        <v>60453</v>
+      </c>
+      <c r="E57" s="7">
+        <v>6868</v>
+      </c>
+      <c r="F57" s="7">
+        <v>13441</v>
+      </c>
+      <c r="G57" s="7">
+        <v>984</v>
+      </c>
+      <c r="H57" s="7">
+        <v>6127</v>
+      </c>
+      <c r="I57" s="7">
+        <v>2587</v>
+      </c>
+      <c r="J57" s="7">
+        <v>3691</v>
+      </c>
+      <c r="K57" s="7">
+        <v>2142</v>
+      </c>
+      <c r="L57" s="7">
+        <v>3258</v>
+      </c>
+      <c r="M57" s="7">
+        <v>3722</v>
+      </c>
+      <c r="N57" s="7">
+        <v>1660</v>
+      </c>
+      <c r="O57" s="7">
+        <v>30011</v>
+      </c>
+      <c r="P57" s="7">
+        <v>1245</v>
+      </c>
+      <c r="Q57" s="7">
+        <v>914</v>
+      </c>
+      <c r="R57" s="7">
+        <v>1565</v>
+      </c>
+      <c r="S57" s="7">
+        <v>8790</v>
+      </c>
+      <c r="T57" s="8">
+        <v>2348</v>
+      </c>
+      <c r="U57" s="7">
+        <v>6049</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <f t="shared" si="1"/>
+        <v>1956</v>
+      </c>
+      <c r="B58" s="7">
+        <v>19250</v>
+      </c>
+      <c r="C58" s="7">
+        <v>3392</v>
+      </c>
+      <c r="D58" s="7">
+        <v>62305</v>
+      </c>
+      <c r="E58" s="7">
+        <v>7052</v>
+      </c>
+      <c r="F58" s="7">
+        <v>13828</v>
+      </c>
+      <c r="G58" s="7">
+        <v>1025</v>
+      </c>
+      <c r="H58" s="7">
+        <v>6256</v>
+      </c>
+      <c r="I58" s="7">
+        <v>2667</v>
+      </c>
+      <c r="J58" s="7">
+        <v>3800</v>
+      </c>
+      <c r="K58" s="7">
+        <v>2210</v>
+      </c>
+      <c r="L58" s="7">
+        <v>3347</v>
+      </c>
+      <c r="M58" s="7">
+        <v>3799</v>
+      </c>
+      <c r="N58" s="7">
+        <v>1712</v>
+      </c>
+      <c r="O58" s="7">
+        <v>30395</v>
+      </c>
+      <c r="P58" s="7">
+        <v>1288</v>
+      </c>
+      <c r="Q58" s="7">
+        <v>940</v>
+      </c>
+      <c r="R58" s="7">
+        <v>1613</v>
+      </c>
+      <c r="S58" s="7">
+        <v>9004</v>
+      </c>
+      <c r="T58" s="8">
+        <v>2375</v>
+      </c>
+      <c r="U58" s="7">
+        <v>6309</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <f t="shared" si="1"/>
+        <v>1957</v>
+      </c>
+      <c r="B59" s="7">
+        <v>19614</v>
+      </c>
+      <c r="C59" s="7">
+        <v>3464</v>
+      </c>
+      <c r="D59" s="7">
+        <v>64227</v>
+      </c>
+      <c r="E59" s="7">
+        <v>7233</v>
+      </c>
+      <c r="F59" s="7">
+        <v>14223</v>
+      </c>
+      <c r="G59" s="7">
+        <v>1068</v>
+      </c>
+      <c r="H59" s="7">
+        <v>6388</v>
+      </c>
+      <c r="I59" s="7">
+        <v>2752</v>
+      </c>
+      <c r="J59" s="7">
+        <v>3929</v>
+      </c>
+      <c r="K59" s="7">
+        <v>2277</v>
+      </c>
+      <c r="L59" s="7">
+        <v>3451</v>
+      </c>
+      <c r="M59" s="7">
+        <v>3873</v>
+      </c>
+      <c r="N59" s="7">
+        <v>1769</v>
+      </c>
+      <c r="O59" s="7">
+        <v>31877</v>
+      </c>
+      <c r="P59" s="7">
+        <v>1332</v>
+      </c>
+      <c r="Q59" s="7">
+        <v>967</v>
+      </c>
+      <c r="R59" s="7">
+        <v>1648</v>
+      </c>
+      <c r="S59" s="7">
+        <v>9235</v>
+      </c>
+      <c r="T59" s="8">
+        <v>2400</v>
+      </c>
+      <c r="U59" s="7">
+        <v>6569</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <f t="shared" si="1"/>
+        <v>1958</v>
+      </c>
+      <c r="B60" s="7">
+        <v>19979</v>
+      </c>
+      <c r="C60" s="7">
+        <v>3539</v>
+      </c>
+      <c r="D60" s="7">
+        <v>66209</v>
+      </c>
+      <c r="E60" s="7">
+        <v>7415</v>
+      </c>
+      <c r="F60" s="7">
+        <v>14627</v>
+      </c>
+      <c r="G60" s="7">
+        <v>1112</v>
+      </c>
+      <c r="H60" s="7">
+        <v>6523</v>
+      </c>
+      <c r="I60" s="7">
+        <v>2840</v>
+      </c>
+      <c r="J60" s="7">
+        <v>4049</v>
+      </c>
+      <c r="K60" s="7">
+        <v>2346</v>
+      </c>
+      <c r="L60" s="7">
+        <v>3546</v>
+      </c>
+      <c r="M60" s="7">
+        <v>3846</v>
+      </c>
+      <c r="N60" s="7">
+        <v>1828</v>
+      </c>
+      <c r="O60" s="7">
+        <v>32868</v>
+      </c>
+      <c r="P60" s="7">
+        <v>1378</v>
+      </c>
+      <c r="Q60" s="7">
+        <v>995</v>
+      </c>
+      <c r="R60" s="7">
+        <v>1687</v>
+      </c>
+      <c r="S60" s="7">
+        <v>9483</v>
+      </c>
+      <c r="T60" s="8">
+        <v>2429</v>
+      </c>
+      <c r="U60" s="7">
+        <v>6829</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <f t="shared" si="1"/>
+        <v>1959</v>
+      </c>
+      <c r="B61" s="7">
+        <v>20325</v>
+      </c>
+      <c r="C61" s="7">
+        <v>3616</v>
+      </c>
+      <c r="D61" s="7">
+        <v>68240</v>
+      </c>
+      <c r="E61" s="7">
+        <v>7599</v>
+      </c>
+      <c r="F61" s="7">
+        <v>15042</v>
+      </c>
+      <c r="G61" s="7">
+        <v>1158</v>
+      </c>
+      <c r="H61" s="7">
+        <v>6661</v>
+      </c>
+      <c r="I61" s="7">
+        <v>2933</v>
+      </c>
+      <c r="J61" s="7">
+        <v>4183</v>
+      </c>
+      <c r="K61" s="7">
+        <v>2416</v>
+      </c>
+      <c r="L61" s="7">
+        <v>3652</v>
+      </c>
+      <c r="M61" s="7">
+        <v>3917</v>
+      </c>
+      <c r="N61" s="7">
+        <v>1887</v>
+      </c>
+      <c r="O61" s="7">
+        <v>33880</v>
+      </c>
+      <c r="P61" s="7">
+        <v>1424</v>
+      </c>
+      <c r="Q61" s="7">
+        <v>1024</v>
+      </c>
+      <c r="R61" s="7">
+        <v>1728</v>
+      </c>
+      <c r="S61" s="7">
+        <v>9746</v>
+      </c>
+      <c r="T61" s="8">
+        <v>2459</v>
+      </c>
+      <c r="U61" s="7">
+        <v>7080</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A62" s="6">
+        <f t="shared" si="1"/>
+        <v>1960</v>
+      </c>
+      <c r="B62" s="7">
+        <v>20669</v>
+      </c>
+      <c r="C62" s="7">
+        <v>3696</v>
+      </c>
+      <c r="D62" s="7">
+        <v>70309</v>
+      </c>
+      <c r="E62" s="7">
+        <v>7791</v>
+      </c>
+      <c r="F62" s="7">
+        <v>15468</v>
+      </c>
+      <c r="G62" s="7">
+        <v>1206</v>
+      </c>
+      <c r="H62" s="7">
+        <v>6797</v>
+      </c>
+      <c r="I62" s="7">
+        <v>3030</v>
+      </c>
+      <c r="J62" s="7">
+        <v>4317</v>
+      </c>
+      <c r="K62" s="7">
+        <v>2490</v>
+      </c>
+      <c r="L62" s="7">
+        <v>3765</v>
+      </c>
+      <c r="M62" s="7">
+        <v>3911</v>
+      </c>
+      <c r="N62" s="7">
+        <v>1950</v>
+      </c>
+      <c r="O62" s="7">
+        <v>34923</v>
+      </c>
+      <c r="P62" s="7">
+        <v>1477</v>
+      </c>
+      <c r="Q62" s="7">
+        <v>1062</v>
+      </c>
+      <c r="R62" s="7">
+        <v>1768</v>
+      </c>
+      <c r="S62" s="7">
+        <v>10025</v>
+      </c>
+      <c r="T62" s="8">
+        <v>2491</v>
+      </c>
+      <c r="U62" s="7">
+        <v>7331</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <f t="shared" si="1"/>
+        <v>1961</v>
+      </c>
+      <c r="B63" s="7">
+        <v>21011</v>
+      </c>
+      <c r="C63" s="7">
+        <v>3778</v>
+      </c>
+      <c r="D63" s="7">
+        <v>72411</v>
+      </c>
+      <c r="E63" s="7">
+        <v>7982</v>
+      </c>
+      <c r="F63" s="7">
+        <v>15908</v>
+      </c>
+      <c r="G63" s="7">
+        <v>1255</v>
+      </c>
+      <c r="H63" s="7">
+        <v>6933</v>
+      </c>
+      <c r="I63" s="7">
+        <v>3132</v>
+      </c>
+      <c r="J63" s="7">
+        <v>4455</v>
+      </c>
+      <c r="K63" s="7">
+        <v>2568</v>
+      </c>
+      <c r="L63" s="7">
+        <v>3868</v>
+      </c>
+      <c r="M63" s="7">
+        <v>4067</v>
+      </c>
+      <c r="N63" s="7">
+        <v>2017</v>
+      </c>
+      <c r="O63" s="7">
+        <v>36075</v>
+      </c>
+      <c r="P63" s="7">
+        <v>1529</v>
+      </c>
+      <c r="Q63" s="7">
+        <v>1095</v>
+      </c>
+      <c r="R63" s="7">
+        <v>1812</v>
+      </c>
+      <c r="S63" s="7">
+        <v>10320</v>
+      </c>
+      <c r="T63" s="8">
+        <v>2523</v>
+      </c>
+      <c r="U63" s="7">
+        <v>7588</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <f t="shared" si="1"/>
+        <v>1962</v>
+      </c>
+      <c r="B64" s="7">
+        <v>21350</v>
+      </c>
+      <c r="C64" s="7">
+        <v>3863</v>
+      </c>
+      <c r="D64" s="7">
+        <v>74544</v>
+      </c>
+      <c r="E64" s="7">
+        <v>8175</v>
+      </c>
+      <c r="F64" s="7">
+        <v>16360</v>
+      </c>
+      <c r="G64" s="7">
+        <v>1305</v>
+      </c>
+      <c r="H64" s="7">
+        <v>7078</v>
+      </c>
+      <c r="I64" s="7">
+        <v>3239</v>
+      </c>
+      <c r="J64" s="7">
+        <v>4579</v>
+      </c>
+      <c r="K64" s="7">
+        <v>2649</v>
+      </c>
+      <c r="L64" s="7">
+        <v>3980</v>
+      </c>
+      <c r="M64" s="7">
+        <v>4145</v>
+      </c>
+      <c r="N64" s="7">
+        <v>2088</v>
+      </c>
+      <c r="O64" s="7">
+        <v>37265</v>
+      </c>
+      <c r="P64" s="7">
+        <v>1583</v>
+      </c>
+      <c r="Q64" s="7">
+        <v>1128</v>
+      </c>
+      <c r="R64" s="7">
+        <v>1858</v>
+      </c>
+      <c r="S64" s="7">
+        <v>10632</v>
+      </c>
+      <c r="T64" s="8">
+        <v>2555</v>
+      </c>
+      <c r="U64" s="7">
+        <v>7858</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <f t="shared" si="1"/>
+        <v>1963</v>
+      </c>
+      <c r="B65" s="7">
+        <v>21688</v>
+      </c>
+      <c r="C65" s="7">
+        <v>3951</v>
+      </c>
+      <c r="D65" s="7">
+        <v>76744</v>
+      </c>
+      <c r="E65" s="7">
+        <v>8371</v>
+      </c>
+      <c r="F65" s="7">
+        <v>16940</v>
+      </c>
+      <c r="G65" s="7">
+        <v>1358</v>
+      </c>
+      <c r="H65" s="7">
+        <v>7224</v>
+      </c>
+      <c r="I65" s="7">
+        <v>3350</v>
+      </c>
+      <c r="J65" s="7">
+        <v>4726</v>
+      </c>
+      <c r="K65" s="7">
+        <v>2734</v>
+      </c>
+      <c r="L65" s="7">
+        <v>4096</v>
+      </c>
+      <c r="M65" s="7">
+        <v>4226</v>
+      </c>
+      <c r="N65" s="7">
+        <v>2161</v>
+      </c>
+      <c r="O65" s="7">
+        <v>39238</v>
+      </c>
+      <c r="P65" s="7">
+        <v>1638</v>
+      </c>
+      <c r="Q65" s="7">
+        <v>1163</v>
+      </c>
+      <c r="R65" s="7">
+        <v>1906</v>
+      </c>
+      <c r="S65" s="7">
+        <v>10958</v>
+      </c>
+      <c r="T65" s="8">
+        <v>2586</v>
+      </c>
+      <c r="U65" s="7">
+        <v>8136</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <f t="shared" si="1"/>
+        <v>1964</v>
+      </c>
+      <c r="B66" s="7">
+        <v>22019</v>
+      </c>
+      <c r="C66" s="7">
+        <v>4042</v>
+      </c>
+      <c r="D66" s="7">
+        <v>78990</v>
+      </c>
+      <c r="E66" s="7">
+        <v>8574</v>
+      </c>
+      <c r="F66" s="7">
+        <v>17485</v>
+      </c>
+      <c r="G66" s="7">
+        <v>1412</v>
+      </c>
+      <c r="H66" s="7">
+        <v>7372</v>
+      </c>
+      <c r="I66" s="7">
+        <v>3466</v>
+      </c>
+      <c r="J66" s="7">
+        <v>4877</v>
+      </c>
+      <c r="K66" s="7">
+        <v>2822</v>
+      </c>
+      <c r="L66" s="7">
+        <v>4217</v>
+      </c>
+      <c r="M66" s="7">
+        <v>4310</v>
+      </c>
+      <c r="N66" s="7">
+        <v>2237</v>
+      </c>
+      <c r="O66" s="7">
+        <v>39781</v>
+      </c>
+      <c r="P66" s="7">
+        <v>1695</v>
+      </c>
+      <c r="Q66" s="7">
+        <v>1198</v>
+      </c>
+      <c r="R66" s="7">
+        <v>1955</v>
+      </c>
+      <c r="S66" s="7">
+        <v>11298</v>
+      </c>
+      <c r="T66" s="8">
+        <v>2617</v>
+      </c>
+      <c r="U66" s="7">
+        <v>8423</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <f t="shared" si="1"/>
+        <v>1965</v>
+      </c>
+      <c r="B67" s="7">
+        <v>22352</v>
+      </c>
+      <c r="C67" s="7">
+        <v>4136</v>
+      </c>
+      <c r="D67" s="7">
+        <v>81300</v>
+      </c>
+      <c r="E67" s="7">
+        <v>8786</v>
+      </c>
+      <c r="F67" s="7">
+        <v>18040</v>
+      </c>
+      <c r="G67" s="7">
+        <v>1467</v>
+      </c>
+      <c r="H67" s="7">
+        <v>7523</v>
+      </c>
+      <c r="I67" s="7">
+        <v>3588</v>
+      </c>
+      <c r="J67" s="7">
+        <v>5036</v>
+      </c>
+      <c r="K67" s="7">
+        <v>2914</v>
+      </c>
+      <c r="L67" s="7">
+        <v>4343</v>
+      </c>
+      <c r="M67" s="7">
+        <v>4396</v>
+      </c>
+      <c r="N67" s="7">
+        <v>2315</v>
+      </c>
+      <c r="O67" s="7">
+        <v>41097</v>
+      </c>
+      <c r="P67" s="7">
+        <v>1754</v>
+      </c>
+      <c r="Q67" s="7">
+        <v>1235</v>
+      </c>
+      <c r="R67" s="7">
+        <v>2007</v>
+      </c>
+      <c r="S67" s="7">
+        <v>11650</v>
+      </c>
+      <c r="T67" s="8">
+        <v>2647</v>
+      </c>
+      <c r="U67" s="7">
+        <v>8722</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <f t="shared" si="1"/>
+        <v>1966</v>
+      </c>
+      <c r="B68" s="7">
+        <v>22691</v>
+      </c>
+      <c r="C68" s="7">
+        <v>4234</v>
+      </c>
+      <c r="D68" s="7">
+        <v>83670</v>
+      </c>
+      <c r="E68" s="7">
+        <v>9007</v>
+      </c>
+      <c r="F68" s="7">
+        <v>18620</v>
+      </c>
+      <c r="G68" s="7">
+        <v>1524</v>
+      </c>
+      <c r="H68" s="7">
+        <v>7675</v>
+      </c>
+      <c r="I68" s="7">
+        <v>3715</v>
+      </c>
+      <c r="J68" s="7">
+        <v>5199</v>
+      </c>
+      <c r="K68" s="7">
+        <v>3008</v>
+      </c>
+      <c r="L68" s="7">
+        <v>4475</v>
+      </c>
+      <c r="M68" s="7">
+        <v>4486</v>
+      </c>
+      <c r="N68" s="7">
+        <v>2396</v>
+      </c>
+      <c r="O68" s="7">
+        <v>42459</v>
+      </c>
+      <c r="P68" s="7">
+        <v>1815</v>
+      </c>
+      <c r="Q68" s="7">
+        <v>1272</v>
+      </c>
+      <c r="R68" s="7">
+        <v>2961</v>
+      </c>
+      <c r="S68" s="7">
+        <v>12012</v>
+      </c>
+      <c r="T68" s="8">
+        <v>2677</v>
+      </c>
+      <c r="U68" s="7">
+        <v>9030</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <f t="shared" si="1"/>
+        <v>1967</v>
+      </c>
+      <c r="B69" s="7">
+        <v>23031</v>
+      </c>
+      <c r="C69" s="7">
+        <v>4334</v>
+      </c>
+      <c r="D69" s="7">
+        <v>86096</v>
+      </c>
+      <c r="E69" s="7">
+        <v>9236</v>
+      </c>
+      <c r="F69" s="7">
+        <v>19220</v>
+      </c>
+      <c r="G69" s="7">
+        <v>1583</v>
+      </c>
+      <c r="H69" s="7">
+        <v>7830</v>
+      </c>
+      <c r="I69" s="7">
+        <v>3846</v>
+      </c>
+      <c r="J69" s="7">
+        <v>5368</v>
+      </c>
+      <c r="K69" s="7">
+        <v>3105</v>
+      </c>
+      <c r="L69" s="7">
+        <v>4611</v>
+      </c>
+      <c r="M69" s="7">
+        <v>4577</v>
+      </c>
+      <c r="N69" s="7">
+        <v>2480</v>
+      </c>
+      <c r="O69" s="7">
+        <v>43863</v>
+      </c>
+      <c r="P69" s="7">
+        <v>1879</v>
+      </c>
+      <c r="Q69" s="7">
+        <v>1311</v>
+      </c>
+      <c r="R69" s="7">
+        <v>2116</v>
+      </c>
+      <c r="S69" s="7">
+        <v>12385</v>
+      </c>
+      <c r="T69" s="8">
+        <v>2709</v>
+      </c>
+      <c r="U69" s="7">
+        <v>9352</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <f t="shared" si="1"/>
+        <v>1968</v>
+      </c>
+      <c r="B70" s="7">
+        <v>23378</v>
+      </c>
+      <c r="C70" s="7">
+        <v>4438</v>
+      </c>
+      <c r="D70" s="7">
+        <v>88582</v>
+      </c>
+      <c r="E70" s="7">
+        <v>9473</v>
+      </c>
+      <c r="F70" s="7">
+        <v>19830</v>
+      </c>
+      <c r="G70" s="7">
+        <v>1643</v>
+      </c>
+      <c r="H70" s="7">
+        <v>7987</v>
+      </c>
+      <c r="I70" s="7">
+        <v>3984</v>
+      </c>
+      <c r="J70" s="7">
+        <v>5543</v>
+      </c>
+      <c r="K70" s="7">
+        <v>3205</v>
+      </c>
+      <c r="L70" s="7">
+        <v>4753</v>
+      </c>
+      <c r="M70" s="7">
+        <v>4671</v>
+      </c>
+      <c r="N70" s="7">
+        <v>2567</v>
+      </c>
+      <c r="O70" s="7">
+        <v>45316</v>
+      </c>
+      <c r="P70" s="7">
+        <v>1945</v>
+      </c>
+      <c r="Q70" s="7">
+        <v>1350</v>
+      </c>
+      <c r="R70" s="7">
+        <v>2174</v>
+      </c>
+      <c r="S70" s="7">
+        <v>12772</v>
+      </c>
+      <c r="T70" s="8">
+        <v>2740</v>
+      </c>
+      <c r="U70" s="7">
+        <v>9686</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <f t="shared" si="1"/>
+        <v>1969</v>
+      </c>
+      <c r="B71" s="7">
+        <v>23706</v>
+      </c>
+      <c r="C71" s="7">
+        <v>4546</v>
+      </c>
+      <c r="D71" s="7">
+        <v>91132</v>
+      </c>
+      <c r="E71" s="7">
+        <v>9717</v>
+      </c>
+      <c r="F71" s="7">
+        <v>20460</v>
+      </c>
+      <c r="G71" s="7">
+        <v>1706</v>
+      </c>
+      <c r="H71" s="7">
+        <v>8145</v>
+      </c>
+      <c r="I71" s="7">
+        <v>4127</v>
+      </c>
+      <c r="J71" s="7">
+        <v>5723</v>
+      </c>
+      <c r="K71" s="7">
+        <v>3309</v>
+      </c>
+      <c r="L71" s="7">
+        <v>4900</v>
+      </c>
+      <c r="M71" s="7">
+        <v>4768</v>
+      </c>
+      <c r="N71" s="7">
+        <v>2657</v>
+      </c>
+      <c r="O71" s="7">
+        <v>46818</v>
+      </c>
+      <c r="P71" s="7">
+        <v>2013</v>
+      </c>
+      <c r="Q71" s="7">
+        <v>1390</v>
+      </c>
+      <c r="R71" s="7">
+        <v>2234</v>
+      </c>
+      <c r="S71" s="7">
+        <v>13172</v>
+      </c>
+      <c r="T71" s="8">
+        <v>2771</v>
+      </c>
+      <c r="U71" s="7">
+        <v>10035</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <f t="shared" si="1"/>
+        <v>1970</v>
+      </c>
+      <c r="B72" s="7">
+        <v>24050</v>
+      </c>
+      <c r="C72" s="7">
+        <v>4658</v>
+      </c>
+      <c r="D72" s="7">
+        <v>93752</v>
+      </c>
+      <c r="E72" s="7">
+        <v>9969</v>
+      </c>
+      <c r="F72" s="7">
+        <v>21120</v>
+      </c>
+      <c r="G72" s="7">
+        <v>1769</v>
+      </c>
+      <c r="H72" s="7">
+        <v>8307</v>
+      </c>
+      <c r="I72" s="7">
+        <v>4277</v>
+      </c>
+      <c r="J72" s="7">
+        <v>5909</v>
+      </c>
+      <c r="K72" s="7">
+        <v>3417</v>
+      </c>
+      <c r="L72" s="7">
+        <v>5053</v>
+      </c>
+      <c r="M72" s="7">
+        <v>4867</v>
+      </c>
+      <c r="N72" s="7">
+        <v>2750</v>
+      </c>
+      <c r="O72" s="7">
+        <v>49090</v>
+      </c>
+      <c r="P72" s="7">
+        <v>2083</v>
+      </c>
+      <c r="Q72" s="7">
+        <v>1432</v>
+      </c>
+      <c r="R72" s="7">
+        <v>2296</v>
+      </c>
+      <c r="S72" s="7">
+        <v>13586</v>
+      </c>
+      <c r="T72" s="8">
+        <v>2802</v>
+      </c>
+      <c r="U72" s="7">
+        <v>10339</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <f t="shared" si="1"/>
+        <v>1971</v>
+      </c>
+      <c r="B73" s="7">
+        <v>24392</v>
+      </c>
+      <c r="C73" s="7">
+        <v>4774</v>
+      </c>
+      <c r="D73" s="7">
+        <v>96443</v>
+      </c>
+      <c r="E73" s="7">
+        <v>10229</v>
+      </c>
+      <c r="F73" s="7">
+        <v>21790</v>
+      </c>
+      <c r="G73" s="7">
+        <v>1834</v>
+      </c>
+      <c r="H73" s="7">
+        <v>8470</v>
+      </c>
+      <c r="I73" s="7">
+        <v>4433</v>
+      </c>
+      <c r="J73" s="7">
+        <v>6102</v>
+      </c>
+      <c r="K73" s="7">
+        <v>3530</v>
+      </c>
+      <c r="L73" s="7">
+        <v>5212</v>
+      </c>
+      <c r="M73" s="7">
+        <v>4969</v>
+      </c>
+      <c r="N73" s="7">
+        <v>2846</v>
+      </c>
+      <c r="O73" s="7">
+        <v>50829</v>
+      </c>
+      <c r="P73" s="7">
+        <v>2156</v>
+      </c>
+      <c r="Q73" s="7">
+        <v>1475</v>
+      </c>
+      <c r="R73" s="7">
+        <v>2361</v>
+      </c>
+      <c r="S73" s="7">
+        <v>14014</v>
+      </c>
+      <c r="T73" s="8">
+        <v>2833</v>
+      </c>
+      <c r="U73" s="7">
+        <v>10777</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <f t="shared" si="1"/>
+        <v>1972</v>
+      </c>
+      <c r="B74" s="7">
+        <v>24745</v>
+      </c>
+      <c r="C74" s="7">
+        <v>4894</v>
+      </c>
+      <c r="D74" s="7">
+        <v>99201</v>
+      </c>
+      <c r="E74" s="7">
+        <v>10498</v>
+      </c>
+      <c r="F74" s="7">
+        <v>22490</v>
+      </c>
+      <c r="G74" s="7">
+        <v>1901</v>
+      </c>
+      <c r="H74" s="7">
+        <v>8636</v>
+      </c>
+      <c r="I74" s="7">
+        <v>4595</v>
+      </c>
+      <c r="J74" s="7">
+        <v>6302</v>
+      </c>
+      <c r="K74" s="7">
+        <v>3647</v>
+      </c>
+      <c r="L74" s="7">
+        <v>5375</v>
+      </c>
+      <c r="M74" s="7">
+        <v>5070</v>
+      </c>
+      <c r="N74" s="7">
+        <v>2946</v>
+      </c>
+      <c r="O74" s="7">
+        <v>52641</v>
+      </c>
+      <c r="P74" s="7">
+        <v>2231</v>
+      </c>
+      <c r="Q74" s="7">
+        <v>1520</v>
+      </c>
+      <c r="R74" s="7">
+        <v>2428</v>
+      </c>
+      <c r="S74" s="7">
+        <v>14456</v>
+      </c>
+      <c r="T74" s="8">
+        <v>2865</v>
+      </c>
+      <c r="U74" s="7">
+        <v>11170</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A76" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A78" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A80" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC009E39-3927-4BA2-A78D-6DA28314788D}">
+  <dimension ref="A1:T30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="9"/>
+      <c r="B1" s="9">
+        <v>1900</v>
+      </c>
+      <c r="C1" s="9">
+        <v>1900</v>
+      </c>
+      <c r="D1" s="9">
+        <v>1910</v>
+      </c>
+      <c r="E1" s="9">
+        <v>1920</v>
+      </c>
+      <c r="F1" s="9">
+        <v>1920</v>
+      </c>
+      <c r="G1" s="9">
+        <v>1930</v>
+      </c>
+      <c r="H1" s="9">
+        <v>1930</v>
+      </c>
+      <c r="I1" s="9">
+        <v>1930</v>
+      </c>
+      <c r="J1" s="9">
+        <v>1940</v>
+      </c>
+      <c r="K1" s="9">
+        <v>1940</v>
+      </c>
+      <c r="L1" s="9">
+        <v>1940</v>
+      </c>
+      <c r="M1" s="9">
+        <v>1950</v>
+      </c>
+      <c r="N1" s="9">
+        <v>1950</v>
+      </c>
+      <c r="O1" s="9">
+        <v>1950</v>
+      </c>
+      <c r="P1" s="9">
+        <v>1960</v>
+      </c>
+      <c r="Q1" s="9">
+        <v>1960</v>
+      </c>
+      <c r="R1" s="9">
+        <v>1960</v>
+      </c>
+      <c r="S1" s="9">
+        <v>1970</v>
+      </c>
+      <c r="T1" s="9">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="S2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="15">
+        <v>31247</v>
+      </c>
+      <c r="C4" s="15">
+        <v>60059</v>
+      </c>
+      <c r="D4" s="16">
+        <v>37981</v>
+      </c>
+      <c r="E4" s="15">
+        <v>43789</v>
+      </c>
+      <c r="F4" s="15">
+        <v>85595</v>
+      </c>
+      <c r="G4" s="15">
+        <v>53672</v>
+      </c>
+      <c r="H4" s="13">
+        <v>102889</v>
+      </c>
+      <c r="I4" s="13">
+        <v>102899</v>
+      </c>
+      <c r="J4" s="15">
+        <v>72735</v>
+      </c>
+      <c r="K4" s="13">
+        <v>124194</v>
+      </c>
+      <c r="L4" s="13">
+        <v>124445</v>
+      </c>
+      <c r="M4" s="15">
+        <v>90345</v>
+      </c>
+      <c r="N4" s="13">
+        <v>157296</v>
+      </c>
+      <c r="O4" s="13">
+        <v>155967</v>
+      </c>
+      <c r="P4" s="15">
+        <v>111489</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>206432</v>
+      </c>
+      <c r="R4" s="13">
+        <v>205018</v>
+      </c>
+      <c r="S4" s="13">
+        <v>274314</v>
+      </c>
+      <c r="T4" s="13">
+        <v>271416</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="13">
+        <v>4556</v>
+      </c>
+      <c r="C5" s="13">
+        <v>4743</v>
+      </c>
+      <c r="D5" s="14">
+        <v>6595</v>
+      </c>
+      <c r="E5" s="13">
+        <v>8749</v>
+      </c>
+      <c r="F5" s="13">
+        <v>8861</v>
+      </c>
+      <c r="G5" s="13">
+        <v>11711</v>
+      </c>
+      <c r="H5" s="13">
+        <v>11896</v>
+      </c>
+      <c r="I5" s="13">
+        <v>11896</v>
+      </c>
+      <c r="J5" s="13">
+        <v>13964</v>
+      </c>
+      <c r="K5" s="13">
+        <v>14169</v>
+      </c>
+      <c r="L5" s="13">
+        <v>14169</v>
+      </c>
+      <c r="M5" s="13">
+        <v>16733</v>
+      </c>
+      <c r="N5" s="13">
+        <v>17085</v>
+      </c>
+      <c r="O5" s="13">
+        <v>17189</v>
+      </c>
+      <c r="P5" s="13">
+        <v>20378</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>20850</v>
+      </c>
+      <c r="R5" s="13">
+        <v>20956</v>
+      </c>
+      <c r="S5" s="13">
+        <v>24352</v>
+      </c>
+      <c r="T5" s="13">
+        <v>24784</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13">
+        <v>1696</v>
+      </c>
+      <c r="D6" s="14"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13">
+        <v>1864</v>
+      </c>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13">
+        <v>2153</v>
+      </c>
+      <c r="I6" s="13">
+        <v>2153</v>
+      </c>
+      <c r="J6" s="13">
+        <v>2052</v>
+      </c>
+      <c r="K6" s="13">
+        <v>2508</v>
+      </c>
+      <c r="L6" s="13">
+        <v>2508</v>
+      </c>
+      <c r="M6" s="13">
+        <v>2670</v>
+      </c>
+      <c r="N6" s="13">
+        <v>3013</v>
+      </c>
+      <c r="O6" s="13">
+        <v>3013</v>
+      </c>
+      <c r="P6" s="13">
+        <v>3044</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>3696</v>
+      </c>
+      <c r="R6" s="13">
+        <v>3696</v>
+      </c>
+      <c r="S6" s="13">
+        <v>4658</v>
+      </c>
+      <c r="T6" s="13">
+        <v>4658</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13">
+        <v>17318</v>
+      </c>
+      <c r="D7" s="14"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13">
+        <v>27554</v>
+      </c>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13">
+        <v>33568</v>
+      </c>
+      <c r="I7" s="13">
+        <v>33718</v>
+      </c>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13">
+        <v>41233</v>
+      </c>
+      <c r="L7" s="13">
+        <v>41525</v>
+      </c>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13">
+        <v>52328</v>
+      </c>
+      <c r="O7" s="13">
+        <v>52328</v>
+      </c>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13">
+        <v>70327</v>
+      </c>
+      <c r="R7" s="13">
+        <v>70459</v>
+      </c>
+      <c r="S7" s="13">
+        <v>93245</v>
+      </c>
+      <c r="T7" s="13">
+        <v>93902</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="13">
+        <v>2856</v>
+      </c>
+      <c r="C8" s="13">
+        <v>2904</v>
+      </c>
+      <c r="D8" s="14">
+        <v>3229</v>
+      </c>
+      <c r="E8" s="13">
+        <v>3664</v>
+      </c>
+      <c r="F8" s="13">
+        <v>3785</v>
+      </c>
+      <c r="G8" s="13">
+        <v>4221</v>
+      </c>
+      <c r="H8" s="13">
+        <v>4424</v>
+      </c>
+      <c r="I8" s="13">
+        <v>4365</v>
+      </c>
+      <c r="J8" s="13">
+        <v>4912</v>
+      </c>
+      <c r="K8" s="13">
+        <v>5147</v>
+      </c>
+      <c r="L8" s="13">
+        <v>5063</v>
+      </c>
+      <c r="M8" s="13">
+        <v>5929</v>
+      </c>
+      <c r="N8" s="13">
+        <v>6058</v>
+      </c>
+      <c r="O8" s="13">
+        <v>6073</v>
+      </c>
+      <c r="P8" s="13">
+        <v>7556</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>7683</v>
+      </c>
+      <c r="R8" s="13">
+        <v>7627</v>
+      </c>
+      <c r="S8" s="13">
+        <v>9117</v>
+      </c>
+      <c r="T8" s="13">
+        <v>9753</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="13">
+        <v>4100</v>
+      </c>
+      <c r="C9" s="13">
+        <v>3825</v>
+      </c>
+      <c r="D9" s="14">
+        <v>4850</v>
+      </c>
+      <c r="E9" s="13">
+        <v>5840</v>
+      </c>
+      <c r="F9" s="13">
+        <v>6089</v>
+      </c>
+      <c r="G9" s="13">
+        <v>7260</v>
+      </c>
+      <c r="H9" s="13">
+        <v>7350</v>
+      </c>
+      <c r="I9" s="13">
+        <v>7280</v>
+      </c>
+      <c r="J9" s="13">
+        <v>8950</v>
+      </c>
+      <c r="K9" s="13">
+        <v>9077</v>
+      </c>
+      <c r="L9" s="13">
+        <v>9097</v>
+      </c>
+      <c r="M9" s="13">
+        <v>11200</v>
+      </c>
+      <c r="N9" s="13">
+        <v>11629</v>
+      </c>
+      <c r="O9" s="13">
+        <v>11679</v>
+      </c>
+      <c r="P9" s="13">
+        <v>14735</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>15877</v>
+      </c>
+      <c r="R9" s="13">
+        <v>15468</v>
+      </c>
+      <c r="S9" s="13">
+        <v>22160</v>
+      </c>
+      <c r="T9" s="13">
+        <v>20514</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="13">
+        <v>254</v>
+      </c>
+      <c r="C10" s="13">
+        <v>285</v>
+      </c>
+      <c r="D10" s="14">
+        <v>325</v>
+      </c>
+      <c r="E10" s="13">
+        <v>399</v>
+      </c>
+      <c r="F10" s="13">
+        <v>421</v>
+      </c>
+      <c r="G10" s="13">
+        <v>501</v>
+      </c>
+      <c r="H10" s="13">
+        <v>499</v>
+      </c>
+      <c r="I10" s="13">
+        <v>499</v>
+      </c>
+      <c r="J10" s="13">
+        <v>637</v>
+      </c>
+      <c r="K10" s="13">
+        <v>619</v>
+      </c>
+      <c r="L10" s="13">
+        <v>619</v>
+      </c>
+      <c r="M10" s="13">
+        <v>841</v>
+      </c>
+      <c r="N10" s="13">
+        <v>849</v>
+      </c>
+      <c r="O10" s="13">
+        <v>801</v>
+      </c>
+      <c r="P10" s="13">
+        <v>1202</v>
+      </c>
+      <c r="Q10" s="13">
+        <v>1249</v>
+      </c>
+      <c r="R10" s="13">
+        <v>1171</v>
+      </c>
+      <c r="S10" s="13">
+        <v>1736</v>
+      </c>
+      <c r="T10" s="13">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="13">
+        <v>1638</v>
+      </c>
+      <c r="C11" s="13">
+        <v>1573</v>
+      </c>
+      <c r="D11" s="14">
+        <v>2192</v>
+      </c>
+      <c r="E11" s="13">
+        <v>2957</v>
+      </c>
+      <c r="F11" s="13">
+        <v>2950</v>
+      </c>
+      <c r="G11" s="13">
+        <v>3828</v>
+      </c>
+      <c r="H11" s="13">
+        <v>3837</v>
+      </c>
+      <c r="I11" s="13">
+        <v>3837</v>
+      </c>
+      <c r="J11" s="13">
+        <v>4449</v>
+      </c>
+      <c r="K11" s="13">
+        <v>4566</v>
+      </c>
+      <c r="L11" s="13">
+        <v>4566</v>
+      </c>
+      <c r="M11" s="13">
+        <v>5513</v>
+      </c>
+      <c r="N11" s="13">
+        <v>5520</v>
+      </c>
+      <c r="O11" s="13">
+        <v>5508</v>
+      </c>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13">
+        <v>6819</v>
+      </c>
+      <c r="R11" s="13">
+        <v>6797</v>
+      </c>
+      <c r="S11" s="13">
+        <v>8341</v>
+      </c>
+      <c r="T11" s="13">
+        <v>8307</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13">
+        <v>700</v>
+      </c>
+      <c r="D12" s="14"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13">
+        <v>1140</v>
+      </c>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13">
+        <v>1400</v>
+      </c>
+      <c r="I12" s="13">
+        <v>1400</v>
+      </c>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13">
+        <v>1759</v>
+      </c>
+      <c r="L12" s="13">
+        <v>1759</v>
+      </c>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13">
+        <v>2303</v>
+      </c>
+      <c r="O12" s="13">
+        <v>2243</v>
+      </c>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13">
+        <v>3129</v>
+      </c>
+      <c r="R12" s="13">
+        <v>3030</v>
+      </c>
+      <c r="S12" s="13">
+        <v>4348</v>
+      </c>
+      <c r="T12" s="13">
+        <v>4277</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13">
+        <v>1400</v>
+      </c>
+      <c r="D13" s="14"/>
+      <c r="E13" s="13">
+        <v>1607</v>
+      </c>
+      <c r="F13" s="13">
+        <v>1930</v>
+      </c>
+      <c r="G13" s="13">
+        <v>1959</v>
+      </c>
+      <c r="H13" s="13">
+        <v>2160</v>
+      </c>
+      <c r="I13" s="13">
+        <v>2102</v>
+      </c>
+      <c r="J13" s="13">
+        <v>2453</v>
+      </c>
+      <c r="K13" s="13">
+        <v>2586</v>
+      </c>
+      <c r="L13" s="13">
+        <v>2546</v>
+      </c>
+      <c r="M13" s="13">
+        <v>3117</v>
+      </c>
+      <c r="N13" s="13">
+        <v>3225</v>
+      </c>
+      <c r="O13" s="13">
+        <v>3277</v>
+      </c>
+      <c r="P13" s="13">
+        <v>4201</v>
+      </c>
+      <c r="Q13" s="13">
+        <v>4323</v>
+      </c>
+      <c r="R13" s="13">
+        <v>4355</v>
+      </c>
+      <c r="S13" s="13">
+        <v>6028</v>
+      </c>
+      <c r="T13" s="13">
+        <v>5819</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="13">
+        <v>943</v>
+      </c>
+      <c r="C14" s="13">
+        <v>932</v>
+      </c>
+      <c r="D14" s="14">
+        <v>1075</v>
+      </c>
+      <c r="E14" s="13">
+        <v>1161</v>
+      </c>
+      <c r="F14" s="13">
+        <v>1168</v>
+      </c>
+      <c r="G14" s="13">
+        <v>1328</v>
+      </c>
+      <c r="H14" s="13">
+        <v>1443</v>
+      </c>
+      <c r="I14" s="13">
+        <v>1350</v>
+      </c>
+      <c r="J14" s="13">
+        <v>1540</v>
+      </c>
+      <c r="K14" s="13">
+        <v>1633</v>
+      </c>
+      <c r="L14" s="13">
+        <v>1550</v>
+      </c>
+      <c r="M14" s="13">
+        <v>1869</v>
+      </c>
+      <c r="N14" s="13">
+        <v>1922</v>
+      </c>
+      <c r="O14" s="13">
+        <v>1868</v>
+      </c>
+      <c r="P14" s="13">
+        <v>2500</v>
+      </c>
+      <c r="Q14" s="13">
+        <v>2512</v>
+      </c>
+      <c r="R14" s="13">
+        <v>2442</v>
+      </c>
+      <c r="S14" s="13">
+        <v>3441</v>
+      </c>
+      <c r="T14" s="13">
+        <v>3346</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="13">
+        <v>1430</v>
+      </c>
+      <c r="C15" s="13">
+        <v>1425</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1580</v>
+      </c>
+      <c r="E15" s="13">
+        <v>1711</v>
+      </c>
+      <c r="F15" s="13">
+        <v>1450</v>
+      </c>
+      <c r="G15" s="13">
+        <v>2000</v>
+      </c>
+      <c r="H15" s="13">
+        <v>1771</v>
+      </c>
+      <c r="I15" s="13">
+        <v>1771</v>
+      </c>
+      <c r="J15" s="13">
+        <v>2300</v>
+      </c>
+      <c r="K15" s="13">
+        <v>2201</v>
+      </c>
+      <c r="L15" s="13">
+        <v>2201</v>
+      </c>
+      <c r="M15" s="13">
+        <v>2800</v>
+      </c>
+      <c r="N15" s="13">
+        <v>3024</v>
+      </c>
+      <c r="O15" s="13">
+        <v>2805</v>
+      </c>
+      <c r="P15" s="13">
+        <v>3715</v>
+      </c>
+      <c r="Q15" s="13">
+        <v>3965</v>
+      </c>
+      <c r="R15" s="13">
+        <v>3765</v>
+      </c>
+      <c r="S15" s="13">
+        <v>5282</v>
+      </c>
+      <c r="T15" s="13">
+        <v>5033</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13">
+        <v>1270</v>
+      </c>
+      <c r="D16" s="14"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13">
+        <v>2124</v>
+      </c>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13">
+        <v>2422</v>
+      </c>
+      <c r="I16" s="13">
+        <v>2422</v>
+      </c>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13">
+        <v>2825</v>
+      </c>
+      <c r="L16" s="13">
+        <v>2827</v>
+      </c>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13">
+        <v>3380</v>
+      </c>
+      <c r="O16" s="13">
+        <v>3380</v>
+      </c>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13">
+        <v>4138</v>
+      </c>
+      <c r="R16" s="13">
+        <v>4140</v>
+      </c>
+      <c r="S16" s="13">
+        <v>5229</v>
+      </c>
+      <c r="T16" s="13">
+        <v>5255</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13">
+        <v>443</v>
+      </c>
+      <c r="D17" s="14">
+        <v>575</v>
+      </c>
+      <c r="E17" s="13">
+        <v>680</v>
+      </c>
+      <c r="F17" s="13">
+        <v>783</v>
+      </c>
+      <c r="G17" s="13">
+        <v>840</v>
+      </c>
+      <c r="H17" s="13">
+        <v>948</v>
+      </c>
+      <c r="I17" s="13">
+        <v>948</v>
+      </c>
+      <c r="J17" s="13">
+        <v>1027</v>
+      </c>
+      <c r="K17" s="13">
+        <v>1119</v>
+      </c>
+      <c r="L17" s="13">
+        <v>1146</v>
+      </c>
+      <c r="M17" s="13">
+        <v>1290</v>
+      </c>
+      <c r="N17" s="13">
+        <v>1389</v>
+      </c>
+      <c r="O17" s="13">
+        <v>1428</v>
+      </c>
+      <c r="P17" s="13">
+        <v>1784</v>
+      </c>
+      <c r="Q17" s="13">
+        <v>1849</v>
+      </c>
+      <c r="R17" s="13">
+        <v>1838</v>
+      </c>
+      <c r="S17" s="13">
+        <v>2583</v>
+      </c>
+      <c r="T17" s="13">
+        <v>2592</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="13">
+        <v>13250</v>
+      </c>
+      <c r="C18" s="13">
+        <v>13607</v>
+      </c>
+      <c r="D18" s="14">
+        <v>15000</v>
+      </c>
+      <c r="E18" s="13">
+        <v>14000</v>
+      </c>
+      <c r="F18" s="13">
+        <v>14500</v>
+      </c>
+      <c r="G18" s="13">
+        <v>16450</v>
+      </c>
+      <c r="H18" s="13">
+        <v>16589</v>
+      </c>
+      <c r="I18" s="13">
+        <v>16589</v>
+      </c>
+      <c r="J18" s="13">
+        <v>19950</v>
+      </c>
+      <c r="K18" s="13">
+        <v>19815</v>
+      </c>
+      <c r="L18" s="13">
+        <v>19815</v>
+      </c>
+      <c r="M18" s="13">
+        <v>25350</v>
+      </c>
+      <c r="N18" s="13">
+        <v>26640</v>
+      </c>
+      <c r="O18" s="13">
+        <v>25826</v>
+      </c>
+      <c r="P18" s="13">
+        <v>34650</v>
+      </c>
+      <c r="Q18" s="13">
+        <v>36046</v>
+      </c>
+      <c r="R18" s="13">
+        <v>34988</v>
+      </c>
+      <c r="S18" s="13">
+        <v>50718</v>
+      </c>
+      <c r="T18" s="13">
+        <v>49282</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13">
+        <v>448</v>
+      </c>
+      <c r="D19" s="14"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13">
+        <v>600</v>
+      </c>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13">
+        <v>742</v>
+      </c>
+      <c r="I19" s="13">
+        <v>700</v>
+      </c>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13">
+        <v>893</v>
+      </c>
+      <c r="L19" s="13">
+        <v>825</v>
+      </c>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13">
+        <v>1133</v>
+      </c>
+      <c r="O19" s="13">
+        <v>1060</v>
+      </c>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13">
+        <v>1501</v>
+      </c>
+      <c r="R19" s="13">
+        <v>1403</v>
+      </c>
+      <c r="S19" s="13">
+        <v>2021</v>
+      </c>
+      <c r="T19" s="13">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="13">
+        <v>227</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14">
+        <v>277</v>
+      </c>
+      <c r="E20" s="13">
+        <v>385</v>
+      </c>
+      <c r="F20" s="13">
+        <v>447</v>
+      </c>
+      <c r="G20" s="13">
+        <v>439</v>
+      </c>
+      <c r="H20" s="13">
+        <v>502</v>
+      </c>
+      <c r="I20" s="13">
+        <v>523</v>
+      </c>
+      <c r="J20" s="13">
+        <v>557</v>
+      </c>
+      <c r="K20" s="13">
+        <v>595</v>
+      </c>
+      <c r="L20" s="13">
+        <v>620</v>
+      </c>
+      <c r="M20" s="13">
+        <v>731</v>
+      </c>
+      <c r="N20" s="13">
+        <v>765</v>
+      </c>
+      <c r="O20" s="13">
+        <v>797</v>
+      </c>
+      <c r="P20" s="13">
+        <v>991</v>
+      </c>
+      <c r="Q20" s="13">
+        <v>1021</v>
+      </c>
+      <c r="R20" s="13">
+        <v>1079</v>
+      </c>
+      <c r="S20" s="13">
+        <v>1406</v>
+      </c>
+      <c r="T20" s="13">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13">
+        <v>440</v>
+      </c>
+      <c r="D21" s="14"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13">
+        <v>699</v>
+      </c>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13">
+        <v>880</v>
+      </c>
+      <c r="I21" s="13">
+        <v>880</v>
+      </c>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13">
+        <v>1111</v>
+      </c>
+      <c r="L21" s="13">
+        <v>1111</v>
+      </c>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13">
+        <v>1337</v>
+      </c>
+      <c r="O21" s="13">
+        <v>1397</v>
+      </c>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13">
+        <v>1740</v>
+      </c>
+      <c r="R21" s="13">
+        <v>1720</v>
+      </c>
+      <c r="S21" s="13">
+        <v>2419</v>
+      </c>
+      <c r="T21" s="13">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13">
+        <v>3791</v>
+      </c>
+      <c r="D22" s="14"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13">
+        <v>5313</v>
+      </c>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13">
+        <v>5651</v>
+      </c>
+      <c r="I22" s="13">
+        <v>5752</v>
+      </c>
+      <c r="J22" s="13">
+        <v>6160</v>
+      </c>
+      <c r="K22" s="13">
+        <v>6681</v>
+      </c>
+      <c r="L22" s="13">
+        <v>6784</v>
+      </c>
+      <c r="M22" s="13">
+        <v>7370</v>
+      </c>
+      <c r="N22" s="13">
+        <v>7968</v>
+      </c>
+      <c r="O22" s="13">
+        <v>8096</v>
+      </c>
+      <c r="P22" s="13">
+        <v>9502</v>
+      </c>
+      <c r="Q22" s="13">
+        <v>10024</v>
+      </c>
+      <c r="R22" s="13">
+        <v>10199</v>
+      </c>
+      <c r="S22" s="13">
+        <v>13586</v>
+      </c>
+      <c r="T22" s="13">
+        <v>13275</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13">
+        <v>915</v>
+      </c>
+      <c r="D23" s="14"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13">
+        <v>1479</v>
+      </c>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13">
+        <v>1734</v>
+      </c>
+      <c r="I23" s="13">
+        <v>1713</v>
+      </c>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13">
+        <v>1947</v>
+      </c>
+      <c r="L23" s="13">
+        <v>1974</v>
+      </c>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13">
+        <v>2198</v>
+      </c>
+      <c r="O23" s="13">
+        <v>2195</v>
+      </c>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13">
+        <v>2542</v>
+      </c>
+      <c r="R23" s="13">
+        <v>2491</v>
+      </c>
+      <c r="S23" s="13">
+        <v>2889</v>
+      </c>
+      <c r="T23" s="13">
+        <v>2802</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="13">
+        <v>1993</v>
+      </c>
+      <c r="C24" s="13">
+        <v>2344</v>
+      </c>
+      <c r="D24" s="14">
+        <v>2283</v>
+      </c>
+      <c r="E24" s="13">
+        <v>2636</v>
+      </c>
+      <c r="F24" s="13">
+        <v>2438</v>
+      </c>
+      <c r="G24" s="13">
+        <v>3135</v>
+      </c>
+      <c r="H24" s="13">
+        <v>2950</v>
+      </c>
+      <c r="I24" s="13">
+        <v>2980</v>
+      </c>
+      <c r="J24" s="13">
+        <v>3784</v>
+      </c>
+      <c r="K24" s="13">
+        <v>3710</v>
+      </c>
+      <c r="L24" s="13">
+        <v>3740</v>
+      </c>
+      <c r="M24" s="13">
+        <v>4932</v>
+      </c>
+      <c r="N24" s="13">
+        <v>5530</v>
+      </c>
+      <c r="O24" s="13">
+        <v>5004</v>
+      </c>
+      <c r="P24" s="13">
+        <v>7231</v>
+      </c>
+      <c r="Q24" s="13">
+        <v>7141</v>
+      </c>
+      <c r="R24" s="13">
+        <v>7394</v>
+      </c>
+      <c r="S24" s="13">
+        <v>10755</v>
+      </c>
+      <c r="T24" s="13">
+        <v>10429</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>